--- a/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>832600</v>
+        <v>858800</v>
       </c>
       <c r="E8" s="3">
-        <v>721100</v>
+        <v>743800</v>
       </c>
       <c r="F8" s="3">
-        <v>576700</v>
+        <v>594900</v>
       </c>
       <c r="G8" s="3">
-        <v>699600</v>
+        <v>721700</v>
       </c>
       <c r="H8" s="3">
-        <v>706800</v>
+        <v>729100</v>
       </c>
       <c r="I8" s="3">
-        <v>581000</v>
+        <v>599400</v>
       </c>
       <c r="J8" s="3">
-        <v>611900</v>
+        <v>631200</v>
       </c>
       <c r="K8" s="3">
         <v>592400</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>343500</v>
+        <v>354300</v>
       </c>
       <c r="E9" s="3">
-        <v>323900</v>
+        <v>334100</v>
       </c>
       <c r="F9" s="3">
-        <v>278100</v>
+        <v>286800</v>
       </c>
       <c r="G9" s="3">
-        <v>323000</v>
+        <v>333100</v>
       </c>
       <c r="H9" s="3">
-        <v>320800</v>
+        <v>330900</v>
       </c>
       <c r="I9" s="3">
-        <v>240000</v>
+        <v>247500</v>
       </c>
       <c r="J9" s="3">
-        <v>273100</v>
+        <v>281700</v>
       </c>
       <c r="K9" s="3">
         <v>312800</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>489100</v>
+        <v>504500</v>
       </c>
       <c r="E10" s="3">
-        <v>397200</v>
+        <v>409700</v>
       </c>
       <c r="F10" s="3">
-        <v>298700</v>
+        <v>308100</v>
       </c>
       <c r="G10" s="3">
-        <v>376700</v>
+        <v>388500</v>
       </c>
       <c r="H10" s="3">
-        <v>386000</v>
+        <v>398200</v>
       </c>
       <c r="I10" s="3">
-        <v>341100</v>
+        <v>351800</v>
       </c>
       <c r="J10" s="3">
-        <v>338900</v>
+        <v>349500</v>
       </c>
       <c r="K10" s="3">
         <v>279700</v>
@@ -993,7 +993,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>355600</v>
+        <v>366800</v>
       </c>
       <c r="E17" s="3">
-        <v>331700</v>
+        <v>342100</v>
       </c>
       <c r="F17" s="3">
-        <v>280700</v>
+        <v>289600</v>
       </c>
       <c r="G17" s="3">
-        <v>326800</v>
+        <v>337100</v>
       </c>
       <c r="H17" s="3">
-        <v>321100</v>
+        <v>331200</v>
       </c>
       <c r="I17" s="3">
-        <v>236800</v>
+        <v>244300</v>
       </c>
       <c r="J17" s="3">
-        <v>269600</v>
+        <v>278100</v>
       </c>
       <c r="K17" s="3">
         <v>307400</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>477000</v>
+        <v>492000</v>
       </c>
       <c r="E18" s="3">
-        <v>389400</v>
+        <v>401700</v>
       </c>
       <c r="F18" s="3">
-        <v>296000</v>
+        <v>305300</v>
       </c>
       <c r="G18" s="3">
-        <v>372800</v>
+        <v>384600</v>
       </c>
       <c r="H18" s="3">
-        <v>385800</v>
+        <v>397900</v>
       </c>
       <c r="I18" s="3">
-        <v>344300</v>
+        <v>355100</v>
       </c>
       <c r="J18" s="3">
-        <v>342300</v>
+        <v>353100</v>
       </c>
       <c r="K18" s="3">
         <v>285000</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-42800</v>
+        <v>-44200</v>
       </c>
       <c r="E20" s="3">
-        <v>12900</v>
+        <v>13300</v>
       </c>
       <c r="F20" s="3">
-        <v>-53200</v>
+        <v>-54900</v>
       </c>
       <c r="G20" s="3">
-        <v>92500</v>
+        <v>95400</v>
       </c>
       <c r="H20" s="3">
-        <v>91800</v>
+        <v>94700</v>
       </c>
       <c r="I20" s="3">
-        <v>44200</v>
+        <v>45500</v>
       </c>
       <c r="J20" s="3">
-        <v>53000</v>
+        <v>54700</v>
       </c>
       <c r="K20" s="3">
         <v>46900</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>504700</v>
+        <v>521100</v>
       </c>
       <c r="E21" s="3">
-        <v>464600</v>
+        <v>479700</v>
       </c>
       <c r="F21" s="3">
-        <v>292600</v>
+        <v>302200</v>
       </c>
       <c r="G21" s="3">
-        <v>505300</v>
+        <v>521500</v>
       </c>
       <c r="H21" s="3">
-        <v>503800</v>
+        <v>519900</v>
       </c>
       <c r="I21" s="3">
-        <v>412900</v>
+        <v>426100</v>
       </c>
       <c r="J21" s="3">
-        <v>416700</v>
+        <v>430000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1245,16 +1245,16 @@
         <v>8</v>
       </c>
       <c r="G22" s="3">
-        <v>53400</v>
+        <v>55000</v>
       </c>
       <c r="H22" s="3">
-        <v>37600</v>
+        <v>38800</v>
       </c>
       <c r="I22" s="3">
-        <v>37800</v>
+        <v>39000</v>
       </c>
       <c r="J22" s="3">
-        <v>68500</v>
+        <v>70700</v>
       </c>
       <c r="K22" s="3">
         <v>41700</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>434200</v>
+        <v>447800</v>
       </c>
       <c r="E23" s="3">
-        <v>402300</v>
+        <v>415000</v>
       </c>
       <c r="F23" s="3">
-        <v>242700</v>
+        <v>250400</v>
       </c>
       <c r="G23" s="3">
-        <v>412000</v>
+        <v>425000</v>
       </c>
       <c r="H23" s="3">
-        <v>439900</v>
+        <v>453800</v>
       </c>
       <c r="I23" s="3">
-        <v>350600</v>
+        <v>361600</v>
       </c>
       <c r="J23" s="3">
-        <v>326800</v>
+        <v>337100</v>
       </c>
       <c r="K23" s="3">
         <v>290200</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>70200</v>
+        <v>72400</v>
       </c>
       <c r="E24" s="3">
-        <v>24600</v>
+        <v>25400</v>
       </c>
       <c r="F24" s="3">
-        <v>44400</v>
+        <v>45800</v>
       </c>
       <c r="G24" s="3">
-        <v>104400</v>
+        <v>107700</v>
       </c>
       <c r="H24" s="3">
-        <v>92500</v>
+        <v>95400</v>
       </c>
       <c r="I24" s="3">
-        <v>70000</v>
+        <v>72200</v>
       </c>
       <c r="J24" s="3">
-        <v>45700</v>
+        <v>47200</v>
       </c>
       <c r="K24" s="3">
         <v>27100</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>363900</v>
+        <v>375400</v>
       </c>
       <c r="E26" s="3">
-        <v>377600</v>
+        <v>389500</v>
       </c>
       <c r="F26" s="3">
-        <v>198400</v>
+        <v>204600</v>
       </c>
       <c r="G26" s="3">
-        <v>307600</v>
+        <v>317300</v>
       </c>
       <c r="H26" s="3">
-        <v>347400</v>
+        <v>358300</v>
       </c>
       <c r="I26" s="3">
-        <v>280600</v>
+        <v>289500</v>
       </c>
       <c r="J26" s="3">
-        <v>281100</v>
+        <v>290000</v>
       </c>
       <c r="K26" s="3">
         <v>263100</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>306300</v>
+        <v>316000</v>
       </c>
       <c r="E27" s="3">
-        <v>325400</v>
+        <v>335700</v>
       </c>
       <c r="F27" s="3">
-        <v>154500</v>
+        <v>159300</v>
       </c>
       <c r="G27" s="3">
-        <v>264800</v>
+        <v>273200</v>
       </c>
       <c r="H27" s="3">
-        <v>303000</v>
+        <v>312600</v>
       </c>
       <c r="I27" s="3">
-        <v>254600</v>
+        <v>262600</v>
       </c>
       <c r="J27" s="3">
-        <v>277800</v>
+        <v>286500</v>
       </c>
       <c r="K27" s="3">
         <v>263000</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>42800</v>
+        <v>44200</v>
       </c>
       <c r="E32" s="3">
-        <v>-12900</v>
+        <v>-13300</v>
       </c>
       <c r="F32" s="3">
-        <v>53200</v>
+        <v>54900</v>
       </c>
       <c r="G32" s="3">
-        <v>-92500</v>
+        <v>-95400</v>
       </c>
       <c r="H32" s="3">
-        <v>-91800</v>
+        <v>-94700</v>
       </c>
       <c r="I32" s="3">
-        <v>-44200</v>
+        <v>-45500</v>
       </c>
       <c r="J32" s="3">
-        <v>-53000</v>
+        <v>-54700</v>
       </c>
       <c r="K32" s="3">
         <v>-46900</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>306300</v>
+        <v>316000</v>
       </c>
       <c r="E33" s="3">
-        <v>325400</v>
+        <v>335700</v>
       </c>
       <c r="F33" s="3">
-        <v>154500</v>
+        <v>159300</v>
       </c>
       <c r="G33" s="3">
-        <v>264800</v>
+        <v>273200</v>
       </c>
       <c r="H33" s="3">
-        <v>303000</v>
+        <v>312600</v>
       </c>
       <c r="I33" s="3">
-        <v>254100</v>
+        <v>262100</v>
       </c>
       <c r="J33" s="3">
-        <v>277800</v>
+        <v>286500</v>
       </c>
       <c r="K33" s="3">
         <v>262000</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>306300</v>
+        <v>316000</v>
       </c>
       <c r="E35" s="3">
-        <v>325400</v>
+        <v>335700</v>
       </c>
       <c r="F35" s="3">
-        <v>154500</v>
+        <v>159300</v>
       </c>
       <c r="G35" s="3">
-        <v>264800</v>
+        <v>273200</v>
       </c>
       <c r="H35" s="3">
-        <v>303000</v>
+        <v>312600</v>
       </c>
       <c r="I35" s="3">
-        <v>254100</v>
+        <v>262100</v>
       </c>
       <c r="J35" s="3">
-        <v>277800</v>
+        <v>286500</v>
       </c>
       <c r="K35" s="3">
         <v>262000</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>49700</v>
+        <v>51300</v>
       </c>
       <c r="E41" s="3">
-        <v>154300</v>
+        <v>159200</v>
       </c>
       <c r="F41" s="3">
-        <v>65800</v>
+        <v>67800</v>
       </c>
       <c r="G41" s="3">
-        <v>28200</v>
+        <v>29100</v>
       </c>
       <c r="H41" s="3">
-        <v>13000</v>
+        <v>13500</v>
       </c>
       <c r="I41" s="3">
-        <v>26500</v>
+        <v>27400</v>
       </c>
       <c r="J41" s="3">
-        <v>892200</v>
+        <v>920300</v>
       </c>
       <c r="K41" s="3">
         <v>580300</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1189100</v>
+        <v>1226600</v>
       </c>
       <c r="E42" s="3">
-        <v>1323200</v>
+        <v>1364900</v>
       </c>
       <c r="F42" s="3">
-        <v>1382900</v>
+        <v>1426500</v>
       </c>
       <c r="G42" s="3">
-        <v>1648800</v>
+        <v>1700700</v>
       </c>
       <c r="H42" s="3">
-        <v>1449600</v>
+        <v>1495300</v>
       </c>
       <c r="I42" s="3">
-        <v>1204800</v>
+        <v>1242800</v>
       </c>
       <c r="J42" s="3">
-        <v>810300</v>
+        <v>835800</v>
       </c>
       <c r="K42" s="3">
         <v>499500</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>145300</v>
+        <v>149900</v>
       </c>
       <c r="E43" s="3">
-        <v>154600</v>
+        <v>159500</v>
       </c>
       <c r="F43" s="3">
-        <v>83000</v>
+        <v>85600</v>
       </c>
       <c r="G43" s="3">
-        <v>97400</v>
+        <v>100500</v>
       </c>
       <c r="H43" s="3">
-        <v>91200</v>
+        <v>94100</v>
       </c>
       <c r="I43" s="3">
-        <v>144000</v>
+        <v>148500</v>
       </c>
       <c r="J43" s="3">
-        <v>259100</v>
+        <v>267300</v>
       </c>
       <c r="K43" s="3">
         <v>174100</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10400</v>
+        <v>10800</v>
       </c>
       <c r="E44" s="3">
-        <v>8900</v>
+        <v>9200</v>
       </c>
       <c r="F44" s="3">
-        <v>7900</v>
+        <v>8200</v>
       </c>
       <c r="G44" s="3">
-        <v>8600</v>
+        <v>8800</v>
       </c>
       <c r="H44" s="3">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="I44" s="3">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="J44" s="3">
-        <v>9200</v>
+        <v>9500</v>
       </c>
       <c r="K44" s="3">
         <v>8000</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>14500</v>
+        <v>15000</v>
       </c>
       <c r="E45" s="3">
-        <v>17500</v>
+        <v>18100</v>
       </c>
       <c r="F45" s="3">
-        <v>13600</v>
+        <v>14100</v>
       </c>
       <c r="G45" s="3">
-        <v>26500</v>
+        <v>27400</v>
       </c>
       <c r="H45" s="3">
-        <v>11400</v>
+        <v>11800</v>
       </c>
       <c r="I45" s="3">
-        <v>29100</v>
+        <v>30000</v>
       </c>
       <c r="J45" s="3">
-        <v>79900</v>
+        <v>82400</v>
       </c>
       <c r="K45" s="3">
         <v>14600</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1409100</v>
+        <v>1453500</v>
       </c>
       <c r="E46" s="3">
-        <v>1658600</v>
+        <v>1710800</v>
       </c>
       <c r="F46" s="3">
-        <v>1553300</v>
+        <v>1602200</v>
       </c>
       <c r="G46" s="3">
-        <v>1812000</v>
+        <v>1869100</v>
       </c>
       <c r="H46" s="3">
-        <v>1575300</v>
+        <v>1625000</v>
       </c>
       <c r="I46" s="3">
-        <v>1410400</v>
+        <v>1454900</v>
       </c>
       <c r="J46" s="3">
-        <v>1028500</v>
+        <v>1061000</v>
       </c>
       <c r="K46" s="3">
         <v>650500</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>181000</v>
+        <v>186700</v>
       </c>
       <c r="E47" s="3">
-        <v>176300</v>
+        <v>181900</v>
       </c>
       <c r="F47" s="3">
-        <v>211200</v>
+        <v>217800</v>
       </c>
       <c r="G47" s="3">
-        <v>111200</v>
+        <v>114700</v>
       </c>
       <c r="H47" s="3">
-        <v>166700</v>
+        <v>171900</v>
       </c>
       <c r="I47" s="3">
-        <v>244800</v>
+        <v>252500</v>
       </c>
       <c r="J47" s="3">
-        <v>224900</v>
+        <v>232000</v>
       </c>
       <c r="K47" s="3">
         <v>199300</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>160900</v>
+        <v>166000</v>
       </c>
       <c r="E48" s="3">
-        <v>143600</v>
+        <v>148100</v>
       </c>
       <c r="F48" s="3">
-        <v>65100</v>
+        <v>67200</v>
       </c>
       <c r="G48" s="3">
-        <v>67200</v>
+        <v>69300</v>
       </c>
       <c r="H48" s="3">
-        <v>60900</v>
+        <v>62800</v>
       </c>
       <c r="I48" s="3">
-        <v>61400</v>
+        <v>63300</v>
       </c>
       <c r="J48" s="3">
-        <v>122900</v>
+        <v>126700</v>
       </c>
       <c r="K48" s="3">
         <v>100100</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2305600</v>
+        <v>2378300</v>
       </c>
       <c r="E49" s="3">
-        <v>2269200</v>
+        <v>2340800</v>
       </c>
       <c r="F49" s="3">
-        <v>2329800</v>
+        <v>2403200</v>
       </c>
       <c r="G49" s="3">
-        <v>2296600</v>
+        <v>2368900</v>
       </c>
       <c r="H49" s="3">
-        <v>2687300</v>
+        <v>2772000</v>
       </c>
       <c r="I49" s="3">
-        <v>1102200</v>
+        <v>1137000</v>
       </c>
       <c r="J49" s="3">
-        <v>1930400</v>
+        <v>1991300</v>
       </c>
       <c r="K49" s="3">
         <v>1692900</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>270400</v>
+        <v>278900</v>
       </c>
       <c r="E52" s="3">
-        <v>213800</v>
+        <v>220500</v>
       </c>
       <c r="F52" s="3">
-        <v>196400</v>
+        <v>202500</v>
       </c>
       <c r="G52" s="3">
-        <v>134500</v>
+        <v>138700</v>
       </c>
       <c r="H52" s="3">
-        <v>115800</v>
+        <v>119400</v>
       </c>
       <c r="I52" s="3">
-        <v>80200</v>
+        <v>82700</v>
       </c>
       <c r="J52" s="3">
-        <v>100200</v>
+        <v>103300</v>
       </c>
       <c r="K52" s="3">
         <v>93500</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4327000</v>
+        <v>4463300</v>
       </c>
       <c r="E54" s="3">
-        <v>4461500</v>
+        <v>4602200</v>
       </c>
       <c r="F54" s="3">
-        <v>4355700</v>
+        <v>4493000</v>
       </c>
       <c r="G54" s="3">
-        <v>4421300</v>
+        <v>4560700</v>
       </c>
       <c r="H54" s="3">
-        <v>3368500</v>
+        <v>3474700</v>
       </c>
       <c r="I54" s="3">
-        <v>2899000</v>
+        <v>2990400</v>
       </c>
       <c r="J54" s="3">
-        <v>2373100</v>
+        <v>2447900</v>
       </c>
       <c r="K54" s="3">
         <v>1814400</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>35800</v>
+        <v>36900</v>
       </c>
       <c r="E57" s="3">
-        <v>34200</v>
+        <v>35300</v>
       </c>
       <c r="F57" s="3">
-        <v>37200</v>
+        <v>38400</v>
       </c>
       <c r="G57" s="3">
-        <v>35700</v>
+        <v>36800</v>
       </c>
       <c r="H57" s="3">
-        <v>24700</v>
+        <v>25500</v>
       </c>
       <c r="I57" s="3">
-        <v>13800</v>
+        <v>14200</v>
       </c>
       <c r="J57" s="3">
-        <v>15100</v>
+        <v>15600</v>
       </c>
       <c r="K57" s="3">
         <v>7800</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>38600</v>
+        <v>39800</v>
       </c>
       <c r="E58" s="3">
-        <v>31400</v>
+        <v>32400</v>
       </c>
       <c r="F58" s="3">
-        <v>23400</v>
+        <v>24100</v>
       </c>
       <c r="G58" s="3">
-        <v>13100</v>
+        <v>13500</v>
       </c>
       <c r="H58" s="3">
-        <v>22200</v>
+        <v>22900</v>
       </c>
       <c r="I58" s="3">
-        <v>41200</v>
+        <v>42500</v>
       </c>
       <c r="J58" s="3">
-        <v>68100</v>
+        <v>70200</v>
       </c>
       <c r="K58" s="3">
         <v>63300</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>210200</v>
+        <v>216900</v>
       </c>
       <c r="E59" s="3">
-        <v>172600</v>
+        <v>178000</v>
       </c>
       <c r="F59" s="3">
-        <v>147000</v>
+        <v>151600</v>
       </c>
       <c r="G59" s="3">
-        <v>309400</v>
+        <v>319200</v>
       </c>
       <c r="H59" s="3">
-        <v>271500</v>
+        <v>280000</v>
       </c>
       <c r="I59" s="3">
-        <v>120800</v>
+        <v>124600</v>
       </c>
       <c r="J59" s="3">
-        <v>124400</v>
+        <v>128300</v>
       </c>
       <c r="K59" s="3">
         <v>190700</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>284600</v>
+        <v>293600</v>
       </c>
       <c r="E60" s="3">
-        <v>238200</v>
+        <v>245700</v>
       </c>
       <c r="F60" s="3">
-        <v>207500</v>
+        <v>214100</v>
       </c>
       <c r="G60" s="3">
-        <v>358200</v>
+        <v>369500</v>
       </c>
       <c r="H60" s="3">
-        <v>318400</v>
+        <v>328400</v>
       </c>
       <c r="I60" s="3">
-        <v>175700</v>
+        <v>181200</v>
       </c>
       <c r="J60" s="3">
-        <v>161300</v>
+        <v>166400</v>
       </c>
       <c r="K60" s="3">
         <v>187100</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>860600</v>
+        <v>887700</v>
       </c>
       <c r="E61" s="3">
-        <v>892400</v>
+        <v>920500</v>
       </c>
       <c r="F61" s="3">
-        <v>918800</v>
+        <v>947800</v>
       </c>
       <c r="G61" s="3">
-        <v>997200</v>
+        <v>1028600</v>
       </c>
       <c r="H61" s="3">
-        <v>385300</v>
+        <v>397400</v>
       </c>
       <c r="I61" s="3">
-        <v>249800</v>
+        <v>257700</v>
       </c>
       <c r="J61" s="3">
-        <v>266200</v>
+        <v>274600</v>
       </c>
       <c r="K61" s="3">
         <v>305800</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>65300</v>
+        <v>67400</v>
       </c>
       <c r="E62" s="3">
-        <v>88200</v>
+        <v>90900</v>
       </c>
       <c r="F62" s="3">
-        <v>147600</v>
+        <v>152300</v>
       </c>
       <c r="G62" s="3">
-        <v>136200</v>
+        <v>140500</v>
       </c>
       <c r="H62" s="3">
-        <v>68600</v>
+        <v>70800</v>
       </c>
       <c r="I62" s="3">
-        <v>11800</v>
+        <v>12200</v>
       </c>
       <c r="J62" s="3">
-        <v>28000</v>
+        <v>28800</v>
       </c>
       <c r="K62" s="3">
         <v>30900</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1650100</v>
+        <v>1702100</v>
       </c>
       <c r="E66" s="3">
-        <v>1666300</v>
+        <v>1718800</v>
       </c>
       <c r="F66" s="3">
-        <v>1699600</v>
+        <v>1753100</v>
       </c>
       <c r="G66" s="3">
-        <v>1905000</v>
+        <v>1965000</v>
       </c>
       <c r="H66" s="3">
-        <v>1050500</v>
+        <v>1083600</v>
       </c>
       <c r="I66" s="3">
-        <v>660900</v>
+        <v>681700</v>
       </c>
       <c r="J66" s="3">
-        <v>575000</v>
+        <v>593200</v>
       </c>
       <c r="K66" s="3">
         <v>524100</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1882000</v>
+        <v>1941300</v>
       </c>
       <c r="E72" s="3">
-        <v>1824700</v>
+        <v>1882200</v>
       </c>
       <c r="F72" s="3">
-        <v>1615300</v>
+        <v>1666300</v>
       </c>
       <c r="G72" s="3">
-        <v>1106600</v>
+        <v>1141500</v>
       </c>
       <c r="H72" s="3">
-        <v>1239700</v>
+        <v>1278700</v>
       </c>
       <c r="I72" s="3">
-        <v>1434600</v>
+        <v>1479800</v>
       </c>
       <c r="J72" s="3">
-        <v>1885900</v>
+        <v>1945400</v>
       </c>
       <c r="K72" s="3">
         <v>1148600</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2676900</v>
+        <v>2761200</v>
       </c>
       <c r="E76" s="3">
-        <v>2795200</v>
+        <v>2883300</v>
       </c>
       <c r="F76" s="3">
-        <v>2656200</v>
+        <v>2739900</v>
       </c>
       <c r="G76" s="3">
-        <v>2516300</v>
+        <v>2595700</v>
       </c>
       <c r="H76" s="3">
-        <v>2318000</v>
+        <v>2391100</v>
       </c>
       <c r="I76" s="3">
-        <v>2238100</v>
+        <v>2308700</v>
       </c>
       <c r="J76" s="3">
-        <v>1798100</v>
+        <v>1854700</v>
       </c>
       <c r="K76" s="3">
         <v>1290300</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>306300</v>
+        <v>316000</v>
       </c>
       <c r="E81" s="3">
-        <v>325400</v>
+        <v>335700</v>
       </c>
       <c r="F81" s="3">
-        <v>154500</v>
+        <v>159300</v>
       </c>
       <c r="G81" s="3">
-        <v>264800</v>
+        <v>273200</v>
       </c>
       <c r="H81" s="3">
-        <v>303000</v>
+        <v>312600</v>
       </c>
       <c r="I81" s="3">
-        <v>254100</v>
+        <v>262100</v>
       </c>
       <c r="J81" s="3">
-        <v>277800</v>
+        <v>286500</v>
       </c>
       <c r="K81" s="3">
         <v>262000</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>70800</v>
+        <v>73100</v>
       </c>
       <c r="E83" s="3">
-        <v>62600</v>
+        <v>64500</v>
       </c>
       <c r="F83" s="3">
-        <v>50100</v>
+        <v>51700</v>
       </c>
       <c r="G83" s="3">
-        <v>40100</v>
+        <v>41400</v>
       </c>
       <c r="H83" s="3">
-        <v>26400</v>
+        <v>27200</v>
       </c>
       <c r="I83" s="3">
-        <v>24600</v>
+        <v>25400</v>
       </c>
       <c r="J83" s="3">
-        <v>21500</v>
+        <v>22200</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>543300</v>
+        <v>560400</v>
       </c>
       <c r="E89" s="3">
-        <v>386500</v>
+        <v>398700</v>
       </c>
       <c r="F89" s="3">
-        <v>238500</v>
+        <v>246000</v>
       </c>
       <c r="G89" s="3">
-        <v>-102500</v>
+        <v>-105700</v>
       </c>
       <c r="H89" s="3">
-        <v>445200</v>
+        <v>459200</v>
       </c>
       <c r="I89" s="3">
-        <v>271000</v>
+        <v>279500</v>
       </c>
       <c r="J89" s="3">
-        <v>346900</v>
+        <v>357900</v>
       </c>
       <c r="K89" s="3">
         <v>269000</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-32500</v>
+        <v>-33500</v>
       </c>
       <c r="E91" s="3">
-        <v>-73700</v>
+        <v>-76000</v>
       </c>
       <c r="F91" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-3800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-3700</v>
-      </c>
       <c r="J91" s="3">
-        <v>-31800</v>
+        <v>-32800</v>
       </c>
       <c r="K91" s="3">
         <v>-10700</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>62500</v>
+        <v>64500</v>
       </c>
       <c r="E94" s="3">
-        <v>70100</v>
+        <v>72300</v>
       </c>
       <c r="F94" s="3">
-        <v>186900</v>
+        <v>192800</v>
       </c>
       <c r="G94" s="3">
-        <v>-59900</v>
+        <v>-61800</v>
       </c>
       <c r="H94" s="3">
-        <v>-294300</v>
+        <v>-303500</v>
       </c>
       <c r="I94" s="3">
-        <v>-502900</v>
+        <v>-518700</v>
       </c>
       <c r="J94" s="3">
-        <v>-442700</v>
+        <v>-456700</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-174200</v>
+        <v>-179700</v>
       </c>
       <c r="E96" s="3">
-        <v>-116100</v>
+        <v>-119800</v>
       </c>
       <c r="F96" s="3">
-        <v>-116100</v>
+        <v>-119800</v>
       </c>
       <c r="G96" s="3">
-        <v>-116100</v>
+        <v>-119800</v>
       </c>
       <c r="H96" s="3">
-        <v>-116100</v>
+        <v>-119800</v>
       </c>
       <c r="I96" s="3">
-        <v>-46400</v>
+        <v>-47900</v>
       </c>
       <c r="J96" s="3">
-        <v>-23200</v>
+        <v>-24000</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-710500</v>
+        <v>-732800</v>
       </c>
       <c r="E100" s="3">
-        <v>-389700</v>
+        <v>-402000</v>
       </c>
       <c r="F100" s="3">
-        <v>-311100</v>
+        <v>-320900</v>
       </c>
       <c r="G100" s="3">
-        <v>203800</v>
+        <v>210200</v>
       </c>
       <c r="H100" s="3">
-        <v>-170900</v>
+        <v>-176300</v>
       </c>
       <c r="I100" s="3">
-        <v>220100</v>
+        <v>227000</v>
       </c>
       <c r="J100" s="3">
-        <v>150000</v>
+        <v>154700</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -4207,22 +4207,22 @@
         <v>8</v>
       </c>
       <c r="E101" s="3">
-        <v>21600</v>
+        <v>22300</v>
       </c>
       <c r="F101" s="3">
-        <v>-76800</v>
+        <v>-79200</v>
       </c>
       <c r="G101" s="3">
-        <v>-26300</v>
+        <v>-27200</v>
       </c>
       <c r="H101" s="3">
-        <v>6400</v>
+        <v>6600</v>
       </c>
       <c r="I101" s="3">
-        <v>394000</v>
+        <v>406400</v>
       </c>
       <c r="J101" s="3">
-        <v>233000</v>
+        <v>240300</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-104600</v>
+        <v>-107900</v>
       </c>
       <c r="E102" s="3">
-        <v>88600</v>
+        <v>91300</v>
       </c>
       <c r="F102" s="3">
-        <v>37600</v>
+        <v>38700</v>
       </c>
       <c r="G102" s="3">
-        <v>15200</v>
+        <v>15600</v>
       </c>
       <c r="H102" s="3">
-        <v>-13600</v>
+        <v>-14000</v>
       </c>
       <c r="I102" s="3">
-        <v>382200</v>
+        <v>394200</v>
       </c>
       <c r="J102" s="3">
-        <v>287200</v>
+        <v>296300</v>
       </c>
       <c r="K102" s="3">
         <v>13400</v>

--- a/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>858800</v>
+        <v>765600</v>
       </c>
       <c r="E8" s="3">
-        <v>743800</v>
+        <v>663100</v>
       </c>
       <c r="F8" s="3">
-        <v>594900</v>
+        <v>530300</v>
       </c>
       <c r="G8" s="3">
-        <v>721700</v>
+        <v>643300</v>
       </c>
       <c r="H8" s="3">
-        <v>729100</v>
+        <v>650000</v>
       </c>
       <c r="I8" s="3">
-        <v>599400</v>
+        <v>534300</v>
       </c>
       <c r="J8" s="3">
-        <v>631200</v>
+        <v>562700</v>
       </c>
       <c r="K8" s="3">
         <v>592400</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>354300</v>
+        <v>315800</v>
       </c>
       <c r="E9" s="3">
-        <v>334100</v>
+        <v>297900</v>
       </c>
       <c r="F9" s="3">
-        <v>286800</v>
+        <v>255700</v>
       </c>
       <c r="G9" s="3">
-        <v>333100</v>
+        <v>297000</v>
       </c>
       <c r="H9" s="3">
-        <v>330900</v>
+        <v>295000</v>
       </c>
       <c r="I9" s="3">
-        <v>247500</v>
+        <v>220700</v>
       </c>
       <c r="J9" s="3">
-        <v>281700</v>
+        <v>251100</v>
       </c>
       <c r="K9" s="3">
         <v>312800</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>504500</v>
+        <v>449800</v>
       </c>
       <c r="E10" s="3">
-        <v>409700</v>
+        <v>365200</v>
       </c>
       <c r="F10" s="3">
-        <v>308100</v>
+        <v>274600</v>
       </c>
       <c r="G10" s="3">
-        <v>388500</v>
+        <v>346400</v>
       </c>
       <c r="H10" s="3">
-        <v>398200</v>
+        <v>355000</v>
       </c>
       <c r="I10" s="3">
-        <v>351800</v>
+        <v>313600</v>
       </c>
       <c r="J10" s="3">
-        <v>349500</v>
+        <v>311600</v>
       </c>
       <c r="K10" s="3">
         <v>279700</v>
@@ -993,7 +993,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
@@ -1005,13 +1005,13 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
         <v>400</v>
       </c>
       <c r="J15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>300</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>366800</v>
+        <v>327000</v>
       </c>
       <c r="E17" s="3">
-        <v>342100</v>
+        <v>305000</v>
       </c>
       <c r="F17" s="3">
-        <v>289600</v>
+        <v>258200</v>
       </c>
       <c r="G17" s="3">
-        <v>337100</v>
+        <v>300500</v>
       </c>
       <c r="H17" s="3">
-        <v>331200</v>
+        <v>295200</v>
       </c>
       <c r="I17" s="3">
-        <v>244300</v>
+        <v>217700</v>
       </c>
       <c r="J17" s="3">
-        <v>278100</v>
+        <v>247900</v>
       </c>
       <c r="K17" s="3">
         <v>307400</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>492000</v>
+        <v>438600</v>
       </c>
       <c r="E18" s="3">
-        <v>401700</v>
+        <v>358100</v>
       </c>
       <c r="F18" s="3">
-        <v>305300</v>
+        <v>272200</v>
       </c>
       <c r="G18" s="3">
-        <v>384600</v>
+        <v>342800</v>
       </c>
       <c r="H18" s="3">
-        <v>397900</v>
+        <v>354700</v>
       </c>
       <c r="I18" s="3">
-        <v>355100</v>
+        <v>316600</v>
       </c>
       <c r="J18" s="3">
-        <v>353100</v>
+        <v>314800</v>
       </c>
       <c r="K18" s="3">
         <v>285000</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-44200</v>
+        <v>-39400</v>
       </c>
       <c r="E20" s="3">
-        <v>13300</v>
+        <v>11800</v>
       </c>
       <c r="F20" s="3">
-        <v>-54900</v>
+        <v>-49000</v>
       </c>
       <c r="G20" s="3">
-        <v>95400</v>
+        <v>85100</v>
       </c>
       <c r="H20" s="3">
-        <v>94700</v>
+        <v>84400</v>
       </c>
       <c r="I20" s="3">
-        <v>45500</v>
+        <v>40600</v>
       </c>
       <c r="J20" s="3">
-        <v>54700</v>
+        <v>48700</v>
       </c>
       <c r="K20" s="3">
         <v>46900</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>521100</v>
+        <v>464900</v>
       </c>
       <c r="E21" s="3">
-        <v>479700</v>
+        <v>428000</v>
       </c>
       <c r="F21" s="3">
-        <v>302200</v>
+        <v>269700</v>
       </c>
       <c r="G21" s="3">
-        <v>521500</v>
+        <v>465100</v>
       </c>
       <c r="H21" s="3">
-        <v>519900</v>
+        <v>463600</v>
       </c>
       <c r="I21" s="3">
-        <v>426100</v>
+        <v>380000</v>
       </c>
       <c r="J21" s="3">
-        <v>430000</v>
+        <v>383500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1245,16 +1245,16 @@
         <v>8</v>
       </c>
       <c r="G22" s="3">
-        <v>55000</v>
+        <v>49100</v>
       </c>
       <c r="H22" s="3">
-        <v>38800</v>
+        <v>34600</v>
       </c>
       <c r="I22" s="3">
-        <v>39000</v>
+        <v>34800</v>
       </c>
       <c r="J22" s="3">
-        <v>70700</v>
+        <v>63000</v>
       </c>
       <c r="K22" s="3">
         <v>41700</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>447800</v>
+        <v>399200</v>
       </c>
       <c r="E23" s="3">
-        <v>415000</v>
+        <v>369900</v>
       </c>
       <c r="F23" s="3">
-        <v>250400</v>
+        <v>223200</v>
       </c>
       <c r="G23" s="3">
-        <v>425000</v>
+        <v>378800</v>
       </c>
       <c r="H23" s="3">
-        <v>453800</v>
+        <v>404500</v>
       </c>
       <c r="I23" s="3">
-        <v>361600</v>
+        <v>322400</v>
       </c>
       <c r="J23" s="3">
-        <v>337100</v>
+        <v>300500</v>
       </c>
       <c r="K23" s="3">
         <v>290200</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>72400</v>
+        <v>64600</v>
       </c>
       <c r="E24" s="3">
-        <v>25400</v>
+        <v>22700</v>
       </c>
       <c r="F24" s="3">
-        <v>45800</v>
+        <v>40800</v>
       </c>
       <c r="G24" s="3">
-        <v>107700</v>
+        <v>96000</v>
       </c>
       <c r="H24" s="3">
-        <v>95400</v>
+        <v>85100</v>
       </c>
       <c r="I24" s="3">
-        <v>72200</v>
+        <v>64300</v>
       </c>
       <c r="J24" s="3">
-        <v>47200</v>
+        <v>42000</v>
       </c>
       <c r="K24" s="3">
         <v>27100</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>375400</v>
+        <v>334700</v>
       </c>
       <c r="E26" s="3">
-        <v>389500</v>
+        <v>347300</v>
       </c>
       <c r="F26" s="3">
-        <v>204600</v>
+        <v>182400</v>
       </c>
       <c r="G26" s="3">
-        <v>317300</v>
+        <v>282800</v>
       </c>
       <c r="H26" s="3">
-        <v>358300</v>
+        <v>319400</v>
       </c>
       <c r="I26" s="3">
-        <v>289500</v>
+        <v>258100</v>
       </c>
       <c r="J26" s="3">
-        <v>290000</v>
+        <v>258500</v>
       </c>
       <c r="K26" s="3">
         <v>263100</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>316000</v>
+        <v>281700</v>
       </c>
       <c r="E27" s="3">
-        <v>335700</v>
+        <v>299300</v>
       </c>
       <c r="F27" s="3">
-        <v>159300</v>
+        <v>142000</v>
       </c>
       <c r="G27" s="3">
-        <v>273200</v>
+        <v>243500</v>
       </c>
       <c r="H27" s="3">
-        <v>312600</v>
+        <v>278600</v>
       </c>
       <c r="I27" s="3">
-        <v>262600</v>
+        <v>234100</v>
       </c>
       <c r="J27" s="3">
-        <v>286500</v>
+        <v>255400</v>
       </c>
       <c r="K27" s="3">
         <v>263000</v>
@@ -1545,7 +1545,7 @@
         <v>8</v>
       </c>
       <c r="I29" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>44200</v>
+        <v>39400</v>
       </c>
       <c r="E32" s="3">
-        <v>-13300</v>
+        <v>-11800</v>
       </c>
       <c r="F32" s="3">
-        <v>54900</v>
+        <v>49000</v>
       </c>
       <c r="G32" s="3">
-        <v>-95400</v>
+        <v>-85100</v>
       </c>
       <c r="H32" s="3">
-        <v>-94700</v>
+        <v>-84400</v>
       </c>
       <c r="I32" s="3">
-        <v>-45500</v>
+        <v>-40600</v>
       </c>
       <c r="J32" s="3">
-        <v>-54700</v>
+        <v>-48700</v>
       </c>
       <c r="K32" s="3">
         <v>-46900</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>316000</v>
+        <v>281700</v>
       </c>
       <c r="E33" s="3">
-        <v>335700</v>
+        <v>299300</v>
       </c>
       <c r="F33" s="3">
-        <v>159300</v>
+        <v>142000</v>
       </c>
       <c r="G33" s="3">
-        <v>273200</v>
+        <v>243500</v>
       </c>
       <c r="H33" s="3">
-        <v>312600</v>
+        <v>278600</v>
       </c>
       <c r="I33" s="3">
-        <v>262100</v>
+        <v>233700</v>
       </c>
       <c r="J33" s="3">
-        <v>286500</v>
+        <v>255400</v>
       </c>
       <c r="K33" s="3">
         <v>262000</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>316000</v>
+        <v>281700</v>
       </c>
       <c r="E35" s="3">
-        <v>335700</v>
+        <v>299300</v>
       </c>
       <c r="F35" s="3">
-        <v>159300</v>
+        <v>142000</v>
       </c>
       <c r="G35" s="3">
-        <v>273200</v>
+        <v>243500</v>
       </c>
       <c r="H35" s="3">
-        <v>312600</v>
+        <v>278600</v>
       </c>
       <c r="I35" s="3">
-        <v>262100</v>
+        <v>233700</v>
       </c>
       <c r="J35" s="3">
-        <v>286500</v>
+        <v>255400</v>
       </c>
       <c r="K35" s="3">
         <v>262000</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>51300</v>
+        <v>45700</v>
       </c>
       <c r="E41" s="3">
-        <v>159200</v>
+        <v>141900</v>
       </c>
       <c r="F41" s="3">
-        <v>67800</v>
+        <v>60500</v>
       </c>
       <c r="G41" s="3">
-        <v>29100</v>
+        <v>25900</v>
       </c>
       <c r="H41" s="3">
-        <v>13500</v>
+        <v>12000</v>
       </c>
       <c r="I41" s="3">
-        <v>27400</v>
+        <v>24400</v>
       </c>
       <c r="J41" s="3">
-        <v>920300</v>
+        <v>820400</v>
       </c>
       <c r="K41" s="3">
         <v>580300</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1226600</v>
+        <v>1093500</v>
       </c>
       <c r="E42" s="3">
-        <v>1364900</v>
+        <v>1216800</v>
       </c>
       <c r="F42" s="3">
-        <v>1426500</v>
+        <v>1271700</v>
       </c>
       <c r="G42" s="3">
-        <v>1700700</v>
+        <v>1516200</v>
       </c>
       <c r="H42" s="3">
-        <v>1495300</v>
+        <v>1333000</v>
       </c>
       <c r="I42" s="3">
-        <v>1242800</v>
+        <v>1107900</v>
       </c>
       <c r="J42" s="3">
-        <v>835800</v>
+        <v>745100</v>
       </c>
       <c r="K42" s="3">
         <v>499500</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>149900</v>
+        <v>133600</v>
       </c>
       <c r="E43" s="3">
-        <v>159500</v>
+        <v>142200</v>
       </c>
       <c r="F43" s="3">
-        <v>85600</v>
+        <v>76300</v>
       </c>
       <c r="G43" s="3">
-        <v>100500</v>
+        <v>89600</v>
       </c>
       <c r="H43" s="3">
-        <v>94100</v>
+        <v>83800</v>
       </c>
       <c r="I43" s="3">
-        <v>148500</v>
+        <v>132400</v>
       </c>
       <c r="J43" s="3">
-        <v>267300</v>
+        <v>238300</v>
       </c>
       <c r="K43" s="3">
         <v>174100</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10800</v>
+        <v>9600</v>
       </c>
       <c r="E44" s="3">
-        <v>9200</v>
+        <v>8200</v>
       </c>
       <c r="F44" s="3">
-        <v>8200</v>
+        <v>7300</v>
       </c>
       <c r="G44" s="3">
-        <v>8800</v>
+        <v>7900</v>
       </c>
       <c r="H44" s="3">
-        <v>7000</v>
+        <v>6200</v>
       </c>
       <c r="I44" s="3">
-        <v>6200</v>
+        <v>5500</v>
       </c>
       <c r="J44" s="3">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="K44" s="3">
         <v>8000</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15000</v>
+        <v>13400</v>
       </c>
       <c r="E45" s="3">
-        <v>18100</v>
+        <v>16100</v>
       </c>
       <c r="F45" s="3">
-        <v>14100</v>
+        <v>12500</v>
       </c>
       <c r="G45" s="3">
-        <v>27400</v>
+        <v>24400</v>
       </c>
       <c r="H45" s="3">
-        <v>11800</v>
+        <v>10500</v>
       </c>
       <c r="I45" s="3">
-        <v>30000</v>
+        <v>26700</v>
       </c>
       <c r="J45" s="3">
-        <v>82400</v>
+        <v>73400</v>
       </c>
       <c r="K45" s="3">
         <v>14600</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1453500</v>
+        <v>1295700</v>
       </c>
       <c r="E46" s="3">
-        <v>1710800</v>
+        <v>1525100</v>
       </c>
       <c r="F46" s="3">
-        <v>1602200</v>
+        <v>1428300</v>
       </c>
       <c r="G46" s="3">
-        <v>1869100</v>
+        <v>1666200</v>
       </c>
       <c r="H46" s="3">
-        <v>1625000</v>
+        <v>1448600</v>
       </c>
       <c r="I46" s="3">
-        <v>1454900</v>
+        <v>1297000</v>
       </c>
       <c r="J46" s="3">
-        <v>1061000</v>
+        <v>945800</v>
       </c>
       <c r="K46" s="3">
         <v>650500</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>186700</v>
+        <v>166400</v>
       </c>
       <c r="E47" s="3">
-        <v>181900</v>
+        <v>162200</v>
       </c>
       <c r="F47" s="3">
-        <v>217800</v>
+        <v>194200</v>
       </c>
       <c r="G47" s="3">
-        <v>114700</v>
+        <v>102200</v>
       </c>
       <c r="H47" s="3">
-        <v>171900</v>
+        <v>153300</v>
       </c>
       <c r="I47" s="3">
-        <v>252500</v>
+        <v>225100</v>
       </c>
       <c r="J47" s="3">
-        <v>232000</v>
+        <v>206800</v>
       </c>
       <c r="K47" s="3">
         <v>199300</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>166000</v>
+        <v>148000</v>
       </c>
       <c r="E48" s="3">
-        <v>148100</v>
+        <v>132000</v>
       </c>
       <c r="F48" s="3">
-        <v>67200</v>
+        <v>59900</v>
       </c>
       <c r="G48" s="3">
-        <v>69300</v>
+        <v>61800</v>
       </c>
       <c r="H48" s="3">
-        <v>62800</v>
+        <v>56000</v>
       </c>
       <c r="I48" s="3">
-        <v>63300</v>
+        <v>56500</v>
       </c>
       <c r="J48" s="3">
-        <v>126700</v>
+        <v>113000</v>
       </c>
       <c r="K48" s="3">
         <v>100100</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2378300</v>
+        <v>2120100</v>
       </c>
       <c r="E49" s="3">
-        <v>2340800</v>
+        <v>2086700</v>
       </c>
       <c r="F49" s="3">
-        <v>2403200</v>
+        <v>2142400</v>
       </c>
       <c r="G49" s="3">
-        <v>2368900</v>
+        <v>2111800</v>
       </c>
       <c r="H49" s="3">
-        <v>2772000</v>
+        <v>2471100</v>
       </c>
       <c r="I49" s="3">
-        <v>1137000</v>
+        <v>1013600</v>
       </c>
       <c r="J49" s="3">
-        <v>1991300</v>
+        <v>1775100</v>
       </c>
       <c r="K49" s="3">
         <v>1692900</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>278900</v>
+        <v>248700</v>
       </c>
       <c r="E52" s="3">
-        <v>220500</v>
+        <v>196600</v>
       </c>
       <c r="F52" s="3">
-        <v>202500</v>
+        <v>180600</v>
       </c>
       <c r="G52" s="3">
-        <v>138700</v>
+        <v>123700</v>
       </c>
       <c r="H52" s="3">
-        <v>119400</v>
+        <v>106500</v>
       </c>
       <c r="I52" s="3">
-        <v>82700</v>
+        <v>73800</v>
       </c>
       <c r="J52" s="3">
-        <v>103300</v>
+        <v>92100</v>
       </c>
       <c r="K52" s="3">
         <v>93500</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4463300</v>
+        <v>3978900</v>
       </c>
       <c r="E54" s="3">
-        <v>4602200</v>
+        <v>4102700</v>
       </c>
       <c r="F54" s="3">
-        <v>4493000</v>
+        <v>4005400</v>
       </c>
       <c r="G54" s="3">
-        <v>4560700</v>
+        <v>4065700</v>
       </c>
       <c r="H54" s="3">
-        <v>3474700</v>
+        <v>3097600</v>
       </c>
       <c r="I54" s="3">
-        <v>2990400</v>
+        <v>2665800</v>
       </c>
       <c r="J54" s="3">
-        <v>2447900</v>
+        <v>2182200</v>
       </c>
       <c r="K54" s="3">
         <v>1814400</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>36900</v>
+        <v>32900</v>
       </c>
       <c r="E57" s="3">
-        <v>35300</v>
+        <v>31500</v>
       </c>
       <c r="F57" s="3">
-        <v>38400</v>
+        <v>34200</v>
       </c>
       <c r="G57" s="3">
-        <v>36800</v>
+        <v>32800</v>
       </c>
       <c r="H57" s="3">
-        <v>25500</v>
+        <v>22700</v>
       </c>
       <c r="I57" s="3">
-        <v>14200</v>
+        <v>12700</v>
       </c>
       <c r="J57" s="3">
-        <v>15600</v>
+        <v>13900</v>
       </c>
       <c r="K57" s="3">
         <v>7800</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>39800</v>
+        <v>35500</v>
       </c>
       <c r="E58" s="3">
-        <v>32400</v>
+        <v>28900</v>
       </c>
       <c r="F58" s="3">
-        <v>24100</v>
+        <v>21500</v>
       </c>
       <c r="G58" s="3">
-        <v>13500</v>
+        <v>12000</v>
       </c>
       <c r="H58" s="3">
-        <v>22900</v>
+        <v>20400</v>
       </c>
       <c r="I58" s="3">
-        <v>42500</v>
+        <v>37800</v>
       </c>
       <c r="J58" s="3">
-        <v>70200</v>
+        <v>62600</v>
       </c>
       <c r="K58" s="3">
         <v>63300</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>216900</v>
+        <v>193300</v>
       </c>
       <c r="E59" s="3">
-        <v>178000</v>
+        <v>158700</v>
       </c>
       <c r="F59" s="3">
-        <v>151600</v>
+        <v>135200</v>
       </c>
       <c r="G59" s="3">
-        <v>319200</v>
+        <v>284500</v>
       </c>
       <c r="H59" s="3">
-        <v>280000</v>
+        <v>249600</v>
       </c>
       <c r="I59" s="3">
-        <v>124600</v>
+        <v>111000</v>
       </c>
       <c r="J59" s="3">
-        <v>128300</v>
+        <v>114400</v>
       </c>
       <c r="K59" s="3">
         <v>190700</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>293600</v>
+        <v>261700</v>
       </c>
       <c r="E60" s="3">
-        <v>245700</v>
+        <v>219100</v>
       </c>
       <c r="F60" s="3">
-        <v>214100</v>
+        <v>190900</v>
       </c>
       <c r="G60" s="3">
-        <v>369500</v>
+        <v>329400</v>
       </c>
       <c r="H60" s="3">
-        <v>328400</v>
+        <v>292800</v>
       </c>
       <c r="I60" s="3">
-        <v>181200</v>
+        <v>161600</v>
       </c>
       <c r="J60" s="3">
-        <v>166400</v>
+        <v>148300</v>
       </c>
       <c r="K60" s="3">
         <v>187100</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>887700</v>
+        <v>791400</v>
       </c>
       <c r="E61" s="3">
-        <v>920500</v>
+        <v>820600</v>
       </c>
       <c r="F61" s="3">
-        <v>947800</v>
+        <v>844900</v>
       </c>
       <c r="G61" s="3">
-        <v>1028600</v>
+        <v>917000</v>
       </c>
       <c r="H61" s="3">
-        <v>397400</v>
+        <v>354300</v>
       </c>
       <c r="I61" s="3">
-        <v>257700</v>
+        <v>229700</v>
       </c>
       <c r="J61" s="3">
-        <v>274600</v>
+        <v>244800</v>
       </c>
       <c r="K61" s="3">
         <v>305800</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>67400</v>
+        <v>60100</v>
       </c>
       <c r="E62" s="3">
-        <v>90900</v>
+        <v>81100</v>
       </c>
       <c r="F62" s="3">
-        <v>152300</v>
+        <v>135700</v>
       </c>
       <c r="G62" s="3">
-        <v>140500</v>
+        <v>125300</v>
       </c>
       <c r="H62" s="3">
-        <v>70800</v>
+        <v>63100</v>
       </c>
       <c r="I62" s="3">
-        <v>12200</v>
+        <v>10900</v>
       </c>
       <c r="J62" s="3">
-        <v>28800</v>
+        <v>25700</v>
       </c>
       <c r="K62" s="3">
         <v>30900</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1702100</v>
+        <v>1517400</v>
       </c>
       <c r="E66" s="3">
-        <v>1718800</v>
+        <v>1532300</v>
       </c>
       <c r="F66" s="3">
-        <v>1753100</v>
+        <v>1562900</v>
       </c>
       <c r="G66" s="3">
-        <v>1965000</v>
+        <v>1751800</v>
       </c>
       <c r="H66" s="3">
-        <v>1083600</v>
+        <v>966000</v>
       </c>
       <c r="I66" s="3">
-        <v>681700</v>
+        <v>607700</v>
       </c>
       <c r="J66" s="3">
-        <v>593200</v>
+        <v>528800</v>
       </c>
       <c r="K66" s="3">
         <v>524100</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1941300</v>
+        <v>1730600</v>
       </c>
       <c r="E72" s="3">
-        <v>1882200</v>
+        <v>1677900</v>
       </c>
       <c r="F72" s="3">
-        <v>1666300</v>
+        <v>1485400</v>
       </c>
       <c r="G72" s="3">
-        <v>1141500</v>
+        <v>1017600</v>
       </c>
       <c r="H72" s="3">
-        <v>1278700</v>
+        <v>1140000</v>
       </c>
       <c r="I72" s="3">
-        <v>1479800</v>
+        <v>1319200</v>
       </c>
       <c r="J72" s="3">
-        <v>1945400</v>
+        <v>1734200</v>
       </c>
       <c r="K72" s="3">
         <v>1148600</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2761200</v>
+        <v>2461600</v>
       </c>
       <c r="E76" s="3">
-        <v>2883300</v>
+        <v>2570400</v>
       </c>
       <c r="F76" s="3">
-        <v>2739900</v>
+        <v>2442500</v>
       </c>
       <c r="G76" s="3">
-        <v>2595700</v>
+        <v>2313900</v>
       </c>
       <c r="H76" s="3">
-        <v>2391100</v>
+        <v>2131600</v>
       </c>
       <c r="I76" s="3">
-        <v>2308700</v>
+        <v>2058100</v>
       </c>
       <c r="J76" s="3">
-        <v>1854700</v>
+        <v>1653400</v>
       </c>
       <c r="K76" s="3">
         <v>1290300</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>316000</v>
+        <v>281700</v>
       </c>
       <c r="E81" s="3">
-        <v>335700</v>
+        <v>299300</v>
       </c>
       <c r="F81" s="3">
-        <v>159300</v>
+        <v>142000</v>
       </c>
       <c r="G81" s="3">
-        <v>273200</v>
+        <v>243500</v>
       </c>
       <c r="H81" s="3">
-        <v>312600</v>
+        <v>278600</v>
       </c>
       <c r="I81" s="3">
-        <v>262100</v>
+        <v>233700</v>
       </c>
       <c r="J81" s="3">
-        <v>286500</v>
+        <v>255400</v>
       </c>
       <c r="K81" s="3">
         <v>262000</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>73100</v>
+        <v>65100</v>
       </c>
       <c r="E83" s="3">
-        <v>64500</v>
+        <v>57500</v>
       </c>
       <c r="F83" s="3">
-        <v>51700</v>
+        <v>46100</v>
       </c>
       <c r="G83" s="3">
-        <v>41400</v>
+        <v>36900</v>
       </c>
       <c r="H83" s="3">
-        <v>27200</v>
+        <v>24300</v>
       </c>
       <c r="I83" s="3">
-        <v>25400</v>
+        <v>22600</v>
       </c>
       <c r="J83" s="3">
-        <v>22200</v>
+        <v>19700</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>560400</v>
+        <v>499600</v>
       </c>
       <c r="E89" s="3">
-        <v>398700</v>
+        <v>355400</v>
       </c>
       <c r="F89" s="3">
-        <v>246000</v>
+        <v>219300</v>
       </c>
       <c r="G89" s="3">
-        <v>-105700</v>
+        <v>-94200</v>
       </c>
       <c r="H89" s="3">
-        <v>459200</v>
+        <v>409400</v>
       </c>
       <c r="I89" s="3">
-        <v>279500</v>
+        <v>249200</v>
       </c>
       <c r="J89" s="3">
-        <v>357900</v>
+        <v>319000</v>
       </c>
       <c r="K89" s="3">
         <v>269000</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-33500</v>
+        <v>-29900</v>
       </c>
       <c r="E91" s="3">
-        <v>-76000</v>
+        <v>-67800</v>
       </c>
       <c r="F91" s="3">
-        <v>-3900</v>
+        <v>-3500</v>
       </c>
       <c r="G91" s="3">
-        <v>-14900</v>
+        <v>-13300</v>
       </c>
       <c r="H91" s="3">
-        <v>-7000</v>
+        <v>-6200</v>
       </c>
       <c r="I91" s="3">
-        <v>-3800</v>
+        <v>-3400</v>
       </c>
       <c r="J91" s="3">
-        <v>-32800</v>
+        <v>-29300</v>
       </c>
       <c r="K91" s="3">
         <v>-10700</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E94" s="3">
         <v>64500</v>
       </c>
-      <c r="E94" s="3">
-        <v>72300</v>
-      </c>
       <c r="F94" s="3">
-        <v>192800</v>
+        <v>171900</v>
       </c>
       <c r="G94" s="3">
-        <v>-61800</v>
+        <v>-55100</v>
       </c>
       <c r="H94" s="3">
-        <v>-303500</v>
+        <v>-270600</v>
       </c>
       <c r="I94" s="3">
-        <v>-518700</v>
+        <v>-462400</v>
       </c>
       <c r="J94" s="3">
-        <v>-456700</v>
+        <v>-407100</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-179700</v>
+        <v>-160200</v>
       </c>
       <c r="E96" s="3">
-        <v>-119800</v>
+        <v>-106800</v>
       </c>
       <c r="F96" s="3">
-        <v>-119800</v>
+        <v>-106800</v>
       </c>
       <c r="G96" s="3">
-        <v>-119800</v>
+        <v>-106800</v>
       </c>
       <c r="H96" s="3">
-        <v>-119800</v>
+        <v>-106800</v>
       </c>
       <c r="I96" s="3">
-        <v>-47900</v>
+        <v>-42700</v>
       </c>
       <c r="J96" s="3">
-        <v>-24000</v>
+        <v>-21400</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-732800</v>
+        <v>-653300</v>
       </c>
       <c r="E100" s="3">
-        <v>-402000</v>
+        <v>-358300</v>
       </c>
       <c r="F100" s="3">
-        <v>-320900</v>
+        <v>-286100</v>
       </c>
       <c r="G100" s="3">
-        <v>210200</v>
+        <v>187400</v>
       </c>
       <c r="H100" s="3">
-        <v>-176300</v>
+        <v>-157100</v>
       </c>
       <c r="I100" s="3">
-        <v>227000</v>
+        <v>202400</v>
       </c>
       <c r="J100" s="3">
-        <v>154700</v>
+        <v>137900</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -4207,22 +4207,22 @@
         <v>8</v>
       </c>
       <c r="E101" s="3">
-        <v>22300</v>
+        <v>19900</v>
       </c>
       <c r="F101" s="3">
-        <v>-79200</v>
+        <v>-70600</v>
       </c>
       <c r="G101" s="3">
-        <v>-27200</v>
+        <v>-24200</v>
       </c>
       <c r="H101" s="3">
-        <v>6600</v>
+        <v>5800</v>
       </c>
       <c r="I101" s="3">
-        <v>406400</v>
+        <v>362300</v>
       </c>
       <c r="J101" s="3">
-        <v>240300</v>
+        <v>214300</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-107900</v>
+        <v>-96200</v>
       </c>
       <c r="E102" s="3">
-        <v>91300</v>
+        <v>81400</v>
       </c>
       <c r="F102" s="3">
-        <v>38700</v>
+        <v>34500</v>
       </c>
       <c r="G102" s="3">
-        <v>15600</v>
+        <v>13900</v>
       </c>
       <c r="H102" s="3">
-        <v>-14000</v>
+        <v>-12500</v>
       </c>
       <c r="I102" s="3">
-        <v>394200</v>
+        <v>351500</v>
       </c>
       <c r="J102" s="3">
-        <v>296300</v>
+        <v>264100</v>
       </c>
       <c r="K102" s="3">
         <v>13400</v>

--- a/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>765600</v>
+        <v>747400</v>
       </c>
       <c r="E8" s="3">
-        <v>663100</v>
+        <v>647300</v>
       </c>
       <c r="F8" s="3">
-        <v>530300</v>
+        <v>517700</v>
       </c>
       <c r="G8" s="3">
-        <v>643300</v>
+        <v>628000</v>
       </c>
       <c r="H8" s="3">
-        <v>650000</v>
+        <v>634500</v>
       </c>
       <c r="I8" s="3">
-        <v>534300</v>
+        <v>521600</v>
       </c>
       <c r="J8" s="3">
-        <v>562700</v>
+        <v>549300</v>
       </c>
       <c r="K8" s="3">
         <v>592400</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>315800</v>
+        <v>308300</v>
       </c>
       <c r="E9" s="3">
-        <v>297900</v>
+        <v>290800</v>
       </c>
       <c r="F9" s="3">
-        <v>255700</v>
+        <v>249600</v>
       </c>
       <c r="G9" s="3">
-        <v>297000</v>
+        <v>289900</v>
       </c>
       <c r="H9" s="3">
-        <v>295000</v>
+        <v>288000</v>
       </c>
       <c r="I9" s="3">
-        <v>220700</v>
+        <v>215400</v>
       </c>
       <c r="J9" s="3">
-        <v>251100</v>
+        <v>245100</v>
       </c>
       <c r="K9" s="3">
         <v>312800</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>449800</v>
+        <v>439100</v>
       </c>
       <c r="E10" s="3">
-        <v>365200</v>
+        <v>356500</v>
       </c>
       <c r="F10" s="3">
-        <v>274600</v>
+        <v>268100</v>
       </c>
       <c r="G10" s="3">
-        <v>346400</v>
+        <v>338100</v>
       </c>
       <c r="H10" s="3">
-        <v>355000</v>
+        <v>346500</v>
       </c>
       <c r="I10" s="3">
-        <v>313600</v>
+        <v>306200</v>
       </c>
       <c r="J10" s="3">
-        <v>311600</v>
+        <v>304200</v>
       </c>
       <c r="K10" s="3">
         <v>279700</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>327000</v>
+        <v>319200</v>
       </c>
       <c r="E17" s="3">
-        <v>305000</v>
+        <v>297800</v>
       </c>
       <c r="F17" s="3">
-        <v>258200</v>
+        <v>252000</v>
       </c>
       <c r="G17" s="3">
-        <v>300500</v>
+        <v>293400</v>
       </c>
       <c r="H17" s="3">
-        <v>295200</v>
+        <v>288200</v>
       </c>
       <c r="I17" s="3">
-        <v>217700</v>
+        <v>212600</v>
       </c>
       <c r="J17" s="3">
-        <v>247900</v>
+        <v>242000</v>
       </c>
       <c r="K17" s="3">
         <v>307400</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>438600</v>
+        <v>428200</v>
       </c>
       <c r="E18" s="3">
-        <v>358100</v>
+        <v>349600</v>
       </c>
       <c r="F18" s="3">
-        <v>272200</v>
+        <v>265700</v>
       </c>
       <c r="G18" s="3">
-        <v>342800</v>
+        <v>334700</v>
       </c>
       <c r="H18" s="3">
-        <v>354700</v>
+        <v>346300</v>
       </c>
       <c r="I18" s="3">
-        <v>316600</v>
+        <v>309000</v>
       </c>
       <c r="J18" s="3">
-        <v>314800</v>
+        <v>307300</v>
       </c>
       <c r="K18" s="3">
         <v>285000</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-39400</v>
+        <v>-38400</v>
       </c>
       <c r="E20" s="3">
-        <v>11800</v>
+        <v>11600</v>
       </c>
       <c r="F20" s="3">
-        <v>-49000</v>
+        <v>-47800</v>
       </c>
       <c r="G20" s="3">
-        <v>85100</v>
+        <v>83000</v>
       </c>
       <c r="H20" s="3">
-        <v>84400</v>
+        <v>82400</v>
       </c>
       <c r="I20" s="3">
-        <v>40600</v>
+        <v>39600</v>
       </c>
       <c r="J20" s="3">
-        <v>48700</v>
+        <v>47600</v>
       </c>
       <c r="K20" s="3">
         <v>46900</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>464900</v>
+        <v>452300</v>
       </c>
       <c r="E21" s="3">
-        <v>428000</v>
+        <v>416400</v>
       </c>
       <c r="F21" s="3">
-        <v>269700</v>
+        <v>262100</v>
       </c>
       <c r="G21" s="3">
-        <v>465100</v>
+        <v>453100</v>
       </c>
       <c r="H21" s="3">
-        <v>463600</v>
+        <v>452000</v>
       </c>
       <c r="I21" s="3">
-        <v>380000</v>
+        <v>370400</v>
       </c>
       <c r="J21" s="3">
-        <v>383500</v>
+        <v>373800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1245,16 +1245,16 @@
         <v>8</v>
       </c>
       <c r="G22" s="3">
-        <v>49100</v>
+        <v>47900</v>
       </c>
       <c r="H22" s="3">
-        <v>34600</v>
+        <v>33800</v>
       </c>
       <c r="I22" s="3">
-        <v>34800</v>
+        <v>33900</v>
       </c>
       <c r="J22" s="3">
-        <v>63000</v>
+        <v>61500</v>
       </c>
       <c r="K22" s="3">
         <v>41700</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>399200</v>
+        <v>389700</v>
       </c>
       <c r="E23" s="3">
-        <v>369900</v>
+        <v>361100</v>
       </c>
       <c r="F23" s="3">
-        <v>223200</v>
+        <v>217900</v>
       </c>
       <c r="G23" s="3">
-        <v>378800</v>
+        <v>369800</v>
       </c>
       <c r="H23" s="3">
-        <v>404500</v>
+        <v>394900</v>
       </c>
       <c r="I23" s="3">
-        <v>322400</v>
+        <v>314700</v>
       </c>
       <c r="J23" s="3">
-        <v>300500</v>
+        <v>293400</v>
       </c>
       <c r="K23" s="3">
         <v>290200</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>64600</v>
+        <v>63000</v>
       </c>
       <c r="E24" s="3">
-        <v>22700</v>
+        <v>22100</v>
       </c>
       <c r="F24" s="3">
-        <v>40800</v>
+        <v>39800</v>
       </c>
       <c r="G24" s="3">
-        <v>96000</v>
+        <v>93700</v>
       </c>
       <c r="H24" s="3">
-        <v>85100</v>
+        <v>83100</v>
       </c>
       <c r="I24" s="3">
-        <v>64300</v>
+        <v>62800</v>
       </c>
       <c r="J24" s="3">
-        <v>42000</v>
+        <v>41000</v>
       </c>
       <c r="K24" s="3">
         <v>27100</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>334700</v>
+        <v>326700</v>
       </c>
       <c r="E26" s="3">
-        <v>347300</v>
+        <v>339000</v>
       </c>
       <c r="F26" s="3">
-        <v>182400</v>
+        <v>178100</v>
       </c>
       <c r="G26" s="3">
-        <v>282800</v>
+        <v>276100</v>
       </c>
       <c r="H26" s="3">
-        <v>319400</v>
+        <v>311800</v>
       </c>
       <c r="I26" s="3">
-        <v>258100</v>
+        <v>251900</v>
       </c>
       <c r="J26" s="3">
-        <v>258500</v>
+        <v>252300</v>
       </c>
       <c r="K26" s="3">
         <v>263100</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>281700</v>
+        <v>275000</v>
       </c>
       <c r="E27" s="3">
-        <v>299300</v>
+        <v>292100</v>
       </c>
       <c r="F27" s="3">
-        <v>142000</v>
+        <v>138700</v>
       </c>
       <c r="G27" s="3">
-        <v>243500</v>
+        <v>237700</v>
       </c>
       <c r="H27" s="3">
-        <v>278600</v>
+        <v>272000</v>
       </c>
       <c r="I27" s="3">
-        <v>234100</v>
+        <v>228500</v>
       </c>
       <c r="J27" s="3">
-        <v>255400</v>
+        <v>249400</v>
       </c>
       <c r="K27" s="3">
         <v>263000</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>39400</v>
+        <v>38400</v>
       </c>
       <c r="E32" s="3">
-        <v>-11800</v>
+        <v>-11600</v>
       </c>
       <c r="F32" s="3">
-        <v>49000</v>
+        <v>47800</v>
       </c>
       <c r="G32" s="3">
-        <v>-85100</v>
+        <v>-83000</v>
       </c>
       <c r="H32" s="3">
-        <v>-84400</v>
+        <v>-82400</v>
       </c>
       <c r="I32" s="3">
-        <v>-40600</v>
+        <v>-39600</v>
       </c>
       <c r="J32" s="3">
-        <v>-48700</v>
+        <v>-47600</v>
       </c>
       <c r="K32" s="3">
         <v>-46900</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>281700</v>
+        <v>275000</v>
       </c>
       <c r="E33" s="3">
-        <v>299300</v>
+        <v>292100</v>
       </c>
       <c r="F33" s="3">
-        <v>142000</v>
+        <v>138700</v>
       </c>
       <c r="G33" s="3">
-        <v>243500</v>
+        <v>237700</v>
       </c>
       <c r="H33" s="3">
-        <v>278600</v>
+        <v>272000</v>
       </c>
       <c r="I33" s="3">
-        <v>233700</v>
+        <v>228100</v>
       </c>
       <c r="J33" s="3">
-        <v>255400</v>
+        <v>249400</v>
       </c>
       <c r="K33" s="3">
         <v>262000</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>281700</v>
+        <v>275000</v>
       </c>
       <c r="E35" s="3">
-        <v>299300</v>
+        <v>292100</v>
       </c>
       <c r="F35" s="3">
-        <v>142000</v>
+        <v>138700</v>
       </c>
       <c r="G35" s="3">
-        <v>243500</v>
+        <v>237700</v>
       </c>
       <c r="H35" s="3">
-        <v>278600</v>
+        <v>272000</v>
       </c>
       <c r="I35" s="3">
-        <v>233700</v>
+        <v>228100</v>
       </c>
       <c r="J35" s="3">
-        <v>255400</v>
+        <v>249400</v>
       </c>
       <c r="K35" s="3">
         <v>262000</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>45700</v>
+        <v>44600</v>
       </c>
       <c r="E41" s="3">
-        <v>141900</v>
+        <v>138500</v>
       </c>
       <c r="F41" s="3">
-        <v>60500</v>
+        <v>59000</v>
       </c>
       <c r="G41" s="3">
-        <v>25900</v>
+        <v>25300</v>
       </c>
       <c r="H41" s="3">
-        <v>12000</v>
+        <v>11700</v>
       </c>
       <c r="I41" s="3">
-        <v>24400</v>
+        <v>23800</v>
       </c>
       <c r="J41" s="3">
-        <v>820400</v>
+        <v>800900</v>
       </c>
       <c r="K41" s="3">
         <v>580300</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1093500</v>
+        <v>1067500</v>
       </c>
       <c r="E42" s="3">
-        <v>1216800</v>
+        <v>1187800</v>
       </c>
       <c r="F42" s="3">
-        <v>1271700</v>
+        <v>1241400</v>
       </c>
       <c r="G42" s="3">
-        <v>1516200</v>
+        <v>1480100</v>
       </c>
       <c r="H42" s="3">
-        <v>1333000</v>
+        <v>1301300</v>
       </c>
       <c r="I42" s="3">
-        <v>1107900</v>
+        <v>1081600</v>
       </c>
       <c r="J42" s="3">
-        <v>745100</v>
+        <v>727400</v>
       </c>
       <c r="K42" s="3">
         <v>499500</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>133600</v>
+        <v>130400</v>
       </c>
       <c r="E43" s="3">
-        <v>142200</v>
+        <v>138800</v>
       </c>
       <c r="F43" s="3">
-        <v>76300</v>
+        <v>74500</v>
       </c>
       <c r="G43" s="3">
-        <v>89600</v>
+        <v>87400</v>
       </c>
       <c r="H43" s="3">
-        <v>83800</v>
+        <v>81900</v>
       </c>
       <c r="I43" s="3">
-        <v>132400</v>
+        <v>129300</v>
       </c>
       <c r="J43" s="3">
-        <v>238300</v>
+        <v>232600</v>
       </c>
       <c r="K43" s="3">
         <v>174100</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="E44" s="3">
-        <v>8200</v>
+        <v>8000</v>
       </c>
       <c r="F44" s="3">
-        <v>7300</v>
+        <v>7100</v>
       </c>
       <c r="G44" s="3">
-        <v>7900</v>
+        <v>7700</v>
       </c>
       <c r="H44" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="I44" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="J44" s="3">
-        <v>8500</v>
+        <v>8300</v>
       </c>
       <c r="K44" s="3">
         <v>8000</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13400</v>
+        <v>13000</v>
       </c>
       <c r="E45" s="3">
-        <v>16100</v>
+        <v>15800</v>
       </c>
       <c r="F45" s="3">
-        <v>12500</v>
+        <v>12200</v>
       </c>
       <c r="G45" s="3">
-        <v>24400</v>
+        <v>23800</v>
       </c>
       <c r="H45" s="3">
-        <v>10500</v>
+        <v>10200</v>
       </c>
       <c r="I45" s="3">
-        <v>26700</v>
+        <v>26100</v>
       </c>
       <c r="J45" s="3">
-        <v>73400</v>
+        <v>71700</v>
       </c>
       <c r="K45" s="3">
         <v>14600</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1295700</v>
+        <v>1264900</v>
       </c>
       <c r="E46" s="3">
-        <v>1525100</v>
+        <v>1488900</v>
       </c>
       <c r="F46" s="3">
-        <v>1428300</v>
+        <v>1394400</v>
       </c>
       <c r="G46" s="3">
-        <v>1666200</v>
+        <v>1626600</v>
       </c>
       <c r="H46" s="3">
-        <v>1448600</v>
+        <v>1414200</v>
       </c>
       <c r="I46" s="3">
-        <v>1297000</v>
+        <v>1266100</v>
       </c>
       <c r="J46" s="3">
-        <v>945800</v>
+        <v>923300</v>
       </c>
       <c r="K46" s="3">
         <v>650500</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>166400</v>
+        <v>162500</v>
       </c>
       <c r="E47" s="3">
-        <v>162200</v>
+        <v>158300</v>
       </c>
       <c r="F47" s="3">
-        <v>194200</v>
+        <v>189600</v>
       </c>
       <c r="G47" s="3">
-        <v>102200</v>
+        <v>99800</v>
       </c>
       <c r="H47" s="3">
-        <v>153300</v>
+        <v>149600</v>
       </c>
       <c r="I47" s="3">
-        <v>225100</v>
+        <v>219700</v>
       </c>
       <c r="J47" s="3">
-        <v>206800</v>
+        <v>201900</v>
       </c>
       <c r="K47" s="3">
         <v>199300</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>148000</v>
+        <v>144400</v>
       </c>
       <c r="E48" s="3">
-        <v>132000</v>
+        <v>128900</v>
       </c>
       <c r="F48" s="3">
-        <v>59900</v>
+        <v>58500</v>
       </c>
       <c r="G48" s="3">
-        <v>61800</v>
+        <v>60300</v>
       </c>
       <c r="H48" s="3">
-        <v>56000</v>
+        <v>54700</v>
       </c>
       <c r="I48" s="3">
-        <v>56500</v>
+        <v>55100</v>
       </c>
       <c r="J48" s="3">
-        <v>113000</v>
+        <v>110300</v>
       </c>
       <c r="K48" s="3">
         <v>100100</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2120100</v>
+        <v>2069700</v>
       </c>
       <c r="E49" s="3">
-        <v>2086700</v>
+        <v>2037100</v>
       </c>
       <c r="F49" s="3">
-        <v>2142400</v>
+        <v>2091400</v>
       </c>
       <c r="G49" s="3">
-        <v>2111800</v>
+        <v>2061600</v>
       </c>
       <c r="H49" s="3">
-        <v>2471100</v>
+        <v>2412300</v>
       </c>
       <c r="I49" s="3">
-        <v>1013600</v>
+        <v>989500</v>
       </c>
       <c r="J49" s="3">
-        <v>1775100</v>
+        <v>1732900</v>
       </c>
       <c r="K49" s="3">
         <v>1692900</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>248700</v>
+        <v>242700</v>
       </c>
       <c r="E52" s="3">
-        <v>196600</v>
+        <v>191900</v>
       </c>
       <c r="F52" s="3">
-        <v>180600</v>
+        <v>176300</v>
       </c>
       <c r="G52" s="3">
-        <v>123700</v>
+        <v>120700</v>
       </c>
       <c r="H52" s="3">
-        <v>106500</v>
+        <v>104000</v>
       </c>
       <c r="I52" s="3">
-        <v>73800</v>
+        <v>72000</v>
       </c>
       <c r="J52" s="3">
-        <v>92100</v>
+        <v>89900</v>
       </c>
       <c r="K52" s="3">
         <v>93500</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3978900</v>
+        <v>3884300</v>
       </c>
       <c r="E54" s="3">
-        <v>4102700</v>
+        <v>4005100</v>
       </c>
       <c r="F54" s="3">
-        <v>4005400</v>
+        <v>3910100</v>
       </c>
       <c r="G54" s="3">
-        <v>4065700</v>
+        <v>3969000</v>
       </c>
       <c r="H54" s="3">
-        <v>3097600</v>
+        <v>3023900</v>
       </c>
       <c r="I54" s="3">
-        <v>2665800</v>
+        <v>2602400</v>
       </c>
       <c r="J54" s="3">
-        <v>2182200</v>
+        <v>2130300</v>
       </c>
       <c r="K54" s="3">
         <v>1814400</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>32900</v>
+        <v>32100</v>
       </c>
       <c r="E57" s="3">
-        <v>31500</v>
+        <v>30700</v>
       </c>
       <c r="F57" s="3">
-        <v>34200</v>
+        <v>33400</v>
       </c>
       <c r="G57" s="3">
-        <v>32800</v>
+        <v>32000</v>
       </c>
       <c r="H57" s="3">
-        <v>22700</v>
+        <v>22200</v>
       </c>
       <c r="I57" s="3">
-        <v>12700</v>
+        <v>12400</v>
       </c>
       <c r="J57" s="3">
-        <v>13900</v>
+        <v>13600</v>
       </c>
       <c r="K57" s="3">
         <v>7800</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>35500</v>
+        <v>34600</v>
       </c>
       <c r="E58" s="3">
-        <v>28900</v>
+        <v>28200</v>
       </c>
       <c r="F58" s="3">
-        <v>21500</v>
+        <v>21000</v>
       </c>
       <c r="G58" s="3">
-        <v>12000</v>
+        <v>11700</v>
       </c>
       <c r="H58" s="3">
-        <v>20400</v>
+        <v>19900</v>
       </c>
       <c r="I58" s="3">
-        <v>37800</v>
+        <v>36900</v>
       </c>
       <c r="J58" s="3">
-        <v>62600</v>
+        <v>61100</v>
       </c>
       <c r="K58" s="3">
         <v>63300</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>193300</v>
+        <v>188700</v>
       </c>
       <c r="E59" s="3">
-        <v>158700</v>
+        <v>154900</v>
       </c>
       <c r="F59" s="3">
-        <v>135200</v>
+        <v>132000</v>
       </c>
       <c r="G59" s="3">
-        <v>284500</v>
+        <v>277800</v>
       </c>
       <c r="H59" s="3">
-        <v>249600</v>
+        <v>243700</v>
       </c>
       <c r="I59" s="3">
-        <v>111000</v>
+        <v>108400</v>
       </c>
       <c r="J59" s="3">
-        <v>114400</v>
+        <v>111700</v>
       </c>
       <c r="K59" s="3">
         <v>190700</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>261700</v>
+        <v>255500</v>
       </c>
       <c r="E60" s="3">
-        <v>219100</v>
+        <v>213800</v>
       </c>
       <c r="F60" s="3">
-        <v>190900</v>
+        <v>186300</v>
       </c>
       <c r="G60" s="3">
-        <v>329400</v>
+        <v>321500</v>
       </c>
       <c r="H60" s="3">
-        <v>292800</v>
+        <v>285800</v>
       </c>
       <c r="I60" s="3">
-        <v>161600</v>
+        <v>157700</v>
       </c>
       <c r="J60" s="3">
-        <v>148300</v>
+        <v>144800</v>
       </c>
       <c r="K60" s="3">
         <v>187100</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>791400</v>
+        <v>772500</v>
       </c>
       <c r="E61" s="3">
-        <v>820600</v>
+        <v>801100</v>
       </c>
       <c r="F61" s="3">
-        <v>844900</v>
+        <v>824800</v>
       </c>
       <c r="G61" s="3">
-        <v>917000</v>
+        <v>895200</v>
       </c>
       <c r="H61" s="3">
-        <v>354300</v>
+        <v>345900</v>
       </c>
       <c r="I61" s="3">
-        <v>229700</v>
+        <v>224300</v>
       </c>
       <c r="J61" s="3">
-        <v>244800</v>
+        <v>239000</v>
       </c>
       <c r="K61" s="3">
         <v>305800</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>60100</v>
+        <v>58600</v>
       </c>
       <c r="E62" s="3">
-        <v>81100</v>
+        <v>79100</v>
       </c>
       <c r="F62" s="3">
-        <v>135700</v>
+        <v>132500</v>
       </c>
       <c r="G62" s="3">
-        <v>125300</v>
+        <v>122300</v>
       </c>
       <c r="H62" s="3">
-        <v>63100</v>
+        <v>61600</v>
       </c>
       <c r="I62" s="3">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="J62" s="3">
-        <v>25700</v>
+        <v>25100</v>
       </c>
       <c r="K62" s="3">
         <v>30900</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1517400</v>
+        <v>1481300</v>
       </c>
       <c r="E66" s="3">
-        <v>1532300</v>
+        <v>1495800</v>
       </c>
       <c r="F66" s="3">
-        <v>1562900</v>
+        <v>1525700</v>
       </c>
       <c r="G66" s="3">
-        <v>1751800</v>
+        <v>1710100</v>
       </c>
       <c r="H66" s="3">
-        <v>966000</v>
+        <v>943000</v>
       </c>
       <c r="I66" s="3">
-        <v>607700</v>
+        <v>593300</v>
       </c>
       <c r="J66" s="3">
-        <v>528800</v>
+        <v>516200</v>
       </c>
       <c r="K66" s="3">
         <v>524100</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1730600</v>
+        <v>1689400</v>
       </c>
       <c r="E72" s="3">
-        <v>1677900</v>
+        <v>1638000</v>
       </c>
       <c r="F72" s="3">
-        <v>1485400</v>
+        <v>1450100</v>
       </c>
       <c r="G72" s="3">
-        <v>1017600</v>
+        <v>993400</v>
       </c>
       <c r="H72" s="3">
-        <v>1140000</v>
+        <v>1112800</v>
       </c>
       <c r="I72" s="3">
-        <v>1319200</v>
+        <v>1287800</v>
       </c>
       <c r="J72" s="3">
-        <v>1734200</v>
+        <v>1693000</v>
       </c>
       <c r="K72" s="3">
         <v>1148600</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2461600</v>
+        <v>2403000</v>
       </c>
       <c r="E76" s="3">
-        <v>2570400</v>
+        <v>2509200</v>
       </c>
       <c r="F76" s="3">
-        <v>2442500</v>
+        <v>2384400</v>
       </c>
       <c r="G76" s="3">
-        <v>2313900</v>
+        <v>2258900</v>
       </c>
       <c r="H76" s="3">
-        <v>2131600</v>
+        <v>2080900</v>
       </c>
       <c r="I76" s="3">
-        <v>2058100</v>
+        <v>2009100</v>
       </c>
       <c r="J76" s="3">
-        <v>1653400</v>
+        <v>1614100</v>
       </c>
       <c r="K76" s="3">
         <v>1290300</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>281700</v>
+        <v>275000</v>
       </c>
       <c r="E81" s="3">
-        <v>299300</v>
+        <v>292100</v>
       </c>
       <c r="F81" s="3">
-        <v>142000</v>
+        <v>138700</v>
       </c>
       <c r="G81" s="3">
-        <v>243500</v>
+        <v>237700</v>
       </c>
       <c r="H81" s="3">
-        <v>278600</v>
+        <v>272000</v>
       </c>
       <c r="I81" s="3">
-        <v>233700</v>
+        <v>228100</v>
       </c>
       <c r="J81" s="3">
-        <v>255400</v>
+        <v>249400</v>
       </c>
       <c r="K81" s="3">
         <v>262000</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>65100</v>
+        <v>63600</v>
       </c>
       <c r="E83" s="3">
-        <v>57500</v>
+        <v>56200</v>
       </c>
       <c r="F83" s="3">
-        <v>46100</v>
+        <v>45000</v>
       </c>
       <c r="G83" s="3">
-        <v>36900</v>
+        <v>36000</v>
       </c>
       <c r="H83" s="3">
-        <v>24300</v>
+        <v>23700</v>
       </c>
       <c r="I83" s="3">
-        <v>22600</v>
+        <v>22100</v>
       </c>
       <c r="J83" s="3">
-        <v>19700</v>
+        <v>19300</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>499600</v>
+        <v>487700</v>
       </c>
       <c r="E89" s="3">
-        <v>355400</v>
+        <v>346900</v>
       </c>
       <c r="F89" s="3">
-        <v>219300</v>
+        <v>214100</v>
       </c>
       <c r="G89" s="3">
-        <v>-94200</v>
+        <v>-92000</v>
       </c>
       <c r="H89" s="3">
-        <v>409400</v>
+        <v>399600</v>
       </c>
       <c r="I89" s="3">
-        <v>249200</v>
+        <v>243300</v>
       </c>
       <c r="J89" s="3">
-        <v>319000</v>
+        <v>311500</v>
       </c>
       <c r="K89" s="3">
         <v>269000</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-29900</v>
+        <v>-29200</v>
       </c>
       <c r="E91" s="3">
-        <v>-67800</v>
+        <v>-66100</v>
       </c>
       <c r="F91" s="3">
-        <v>-3500</v>
+        <v>-3400</v>
       </c>
       <c r="G91" s="3">
-        <v>-13300</v>
+        <v>-13000</v>
       </c>
       <c r="H91" s="3">
-        <v>-6200</v>
+        <v>-6100</v>
       </c>
       <c r="I91" s="3">
-        <v>-3400</v>
+        <v>-3300</v>
       </c>
       <c r="J91" s="3">
-        <v>-29300</v>
+        <v>-28600</v>
       </c>
       <c r="K91" s="3">
         <v>-10700</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>57500</v>
+        <v>56100</v>
       </c>
       <c r="E94" s="3">
-        <v>64500</v>
+        <v>62900</v>
       </c>
       <c r="F94" s="3">
-        <v>171900</v>
+        <v>167800</v>
       </c>
       <c r="G94" s="3">
-        <v>-55100</v>
+        <v>-53800</v>
       </c>
       <c r="H94" s="3">
-        <v>-270600</v>
+        <v>-264200</v>
       </c>
       <c r="I94" s="3">
-        <v>-462400</v>
+        <v>-451400</v>
       </c>
       <c r="J94" s="3">
-        <v>-407100</v>
+        <v>-397400</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-160200</v>
+        <v>-156400</v>
       </c>
       <c r="E96" s="3">
-        <v>-106800</v>
+        <v>-104200</v>
       </c>
       <c r="F96" s="3">
-        <v>-106800</v>
+        <v>-104200</v>
       </c>
       <c r="G96" s="3">
-        <v>-106800</v>
+        <v>-104200</v>
       </c>
       <c r="H96" s="3">
-        <v>-106800</v>
+        <v>-104200</v>
       </c>
       <c r="I96" s="3">
-        <v>-42700</v>
+        <v>-41700</v>
       </c>
       <c r="J96" s="3">
-        <v>-21400</v>
+        <v>-20800</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-653300</v>
+        <v>-637800</v>
       </c>
       <c r="E100" s="3">
-        <v>-358300</v>
+        <v>-349800</v>
       </c>
       <c r="F100" s="3">
-        <v>-286100</v>
+        <v>-279300</v>
       </c>
       <c r="G100" s="3">
-        <v>187400</v>
+        <v>183000</v>
       </c>
       <c r="H100" s="3">
-        <v>-157100</v>
+        <v>-153400</v>
       </c>
       <c r="I100" s="3">
-        <v>202400</v>
+        <v>197600</v>
       </c>
       <c r="J100" s="3">
-        <v>137900</v>
+        <v>134600</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -4207,22 +4207,22 @@
         <v>8</v>
       </c>
       <c r="E101" s="3">
-        <v>19900</v>
+        <v>19400</v>
       </c>
       <c r="F101" s="3">
-        <v>-70600</v>
+        <v>-68900</v>
       </c>
       <c r="G101" s="3">
-        <v>-24200</v>
+        <v>-23600</v>
       </c>
       <c r="H101" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="I101" s="3">
-        <v>362300</v>
+        <v>353700</v>
       </c>
       <c r="J101" s="3">
-        <v>214300</v>
+        <v>209200</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-96200</v>
+        <v>-93900</v>
       </c>
       <c r="E102" s="3">
-        <v>81400</v>
+        <v>79500</v>
       </c>
       <c r="F102" s="3">
-        <v>34500</v>
+        <v>33700</v>
       </c>
       <c r="G102" s="3">
-        <v>13900</v>
+        <v>13600</v>
       </c>
       <c r="H102" s="3">
-        <v>-12500</v>
+        <v>-12200</v>
       </c>
       <c r="I102" s="3">
-        <v>351500</v>
+        <v>343100</v>
       </c>
       <c r="J102" s="3">
-        <v>264100</v>
+        <v>257800</v>
       </c>
       <c r="K102" s="3">
         <v>13400</v>

--- a/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>PUODY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>747400</v>
+        <v>918700</v>
       </c>
       <c r="E8" s="3">
-        <v>647300</v>
+        <v>735200</v>
       </c>
       <c r="F8" s="3">
-        <v>517700</v>
+        <v>605800</v>
       </c>
       <c r="G8" s="3">
-        <v>628000</v>
+        <v>499200</v>
       </c>
       <c r="H8" s="3">
-        <v>634500</v>
+        <v>638900</v>
       </c>
       <c r="I8" s="3">
-        <v>521600</v>
+        <v>619500</v>
       </c>
       <c r="J8" s="3">
+        <v>509800</v>
+      </c>
+      <c r="K8" s="3">
         <v>549300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>592400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>334500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>281600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>206700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>215400</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>308300</v>
+        <v>332000</v>
       </c>
       <c r="E9" s="3">
-        <v>290800</v>
+        <v>303500</v>
       </c>
       <c r="F9" s="3">
-        <v>249600</v>
+        <v>272300</v>
       </c>
       <c r="G9" s="3">
-        <v>289900</v>
+        <v>240800</v>
       </c>
       <c r="H9" s="3">
-        <v>288000</v>
+        <v>295200</v>
       </c>
       <c r="I9" s="3">
-        <v>215400</v>
+        <v>281400</v>
       </c>
       <c r="J9" s="3">
+        <v>210800</v>
+      </c>
+      <c r="K9" s="3">
         <v>245100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>312800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>152200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>120800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>81100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>86000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>439100</v>
+        <v>586700</v>
       </c>
       <c r="E10" s="3">
-        <v>356500</v>
+        <v>431700</v>
       </c>
       <c r="F10" s="3">
-        <v>268100</v>
+        <v>333500</v>
       </c>
       <c r="G10" s="3">
-        <v>338100</v>
+        <v>258400</v>
       </c>
       <c r="H10" s="3">
-        <v>346500</v>
+        <v>343700</v>
       </c>
       <c r="I10" s="3">
-        <v>306200</v>
+        <v>338200</v>
       </c>
       <c r="J10" s="3">
+        <v>299000</v>
+      </c>
+      <c r="K10" s="3">
         <v>304200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>279700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>182300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>160800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>125700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>129400</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,32 +960,35 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>3300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -986,39 +1005,42 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
       </c>
       <c r="F15" s="3">
+        <v>500</v>
+      </c>
+      <c r="G15" s="3">
         <v>300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>500</v>
       </c>
-      <c r="I15" s="3">
-        <v>400</v>
-      </c>
       <c r="J15" s="3">
+        <v>21600</v>
+      </c>
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>319200</v>
+        <v>337200</v>
       </c>
       <c r="E17" s="3">
-        <v>297800</v>
+        <v>314000</v>
       </c>
       <c r="F17" s="3">
-        <v>252000</v>
+        <v>278700</v>
       </c>
       <c r="G17" s="3">
-        <v>293400</v>
+        <v>243000</v>
       </c>
       <c r="H17" s="3">
-        <v>288200</v>
+        <v>298400</v>
       </c>
       <c r="I17" s="3">
-        <v>212600</v>
+        <v>281400</v>
       </c>
       <c r="J17" s="3">
+        <v>207800</v>
+      </c>
+      <c r="K17" s="3">
         <v>242000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>307400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>146300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>118600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>81800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>87700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>428200</v>
+        <v>581600</v>
       </c>
       <c r="E18" s="3">
-        <v>349600</v>
+        <v>421200</v>
       </c>
       <c r="F18" s="3">
-        <v>265700</v>
+        <v>327200</v>
       </c>
       <c r="G18" s="3">
-        <v>334700</v>
+        <v>256200</v>
       </c>
       <c r="H18" s="3">
-        <v>346300</v>
+        <v>340500</v>
       </c>
       <c r="I18" s="3">
-        <v>309000</v>
+        <v>338100</v>
       </c>
       <c r="J18" s="3">
+        <v>302000</v>
+      </c>
+      <c r="K18" s="3">
         <v>307300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>285000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>188100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>163000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>125000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>127700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,77 +1178,81 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-38400</v>
+        <v>95700</v>
       </c>
       <c r="E20" s="3">
-        <v>11600</v>
+        <v>42900</v>
       </c>
       <c r="F20" s="3">
-        <v>-47800</v>
+        <v>-21300</v>
       </c>
       <c r="G20" s="3">
-        <v>83000</v>
+        <v>68500</v>
       </c>
       <c r="H20" s="3">
-        <v>82400</v>
+        <v>18100</v>
       </c>
       <c r="I20" s="3">
-        <v>39600</v>
+        <v>-11400</v>
       </c>
       <c r="J20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K20" s="3">
         <v>47600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>46900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>19800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-55500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>452300</v>
+        <v>486600</v>
       </c>
       <c r="E21" s="3">
-        <v>416400</v>
+        <v>378900</v>
       </c>
       <c r="F21" s="3">
-        <v>262100</v>
+        <v>348900</v>
       </c>
       <c r="G21" s="3">
-        <v>453100</v>
+        <v>187900</v>
       </c>
       <c r="H21" s="3">
-        <v>452000</v>
+        <v>322500</v>
       </c>
       <c r="I21" s="3">
-        <v>370400</v>
+        <v>350000</v>
       </c>
       <c r="J21" s="3">
+        <v>328600</v>
+      </c>
+      <c r="K21" s="3">
         <v>373800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1229,135 +1265,147 @@
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>151100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>154700</v>
+      </c>
+      <c r="F22" s="3">
+        <v>124000</v>
       </c>
       <c r="G22" s="3">
-        <v>47900</v>
+        <v>71200</v>
       </c>
       <c r="H22" s="3">
-        <v>33800</v>
+        <v>57600</v>
       </c>
       <c r="I22" s="3">
-        <v>33900</v>
+        <v>33000</v>
       </c>
       <c r="J22" s="3">
+        <v>33200</v>
+      </c>
+      <c r="K22" s="3">
         <v>61500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>41700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>79200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>54800</v>
       </c>
       <c r="N22" s="3">
         <v>54800</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>54800</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>389700</v>
+        <v>550200</v>
       </c>
       <c r="E23" s="3">
-        <v>361100</v>
+        <v>383400</v>
       </c>
       <c r="F23" s="3">
-        <v>217900</v>
+        <v>338000</v>
       </c>
       <c r="G23" s="3">
-        <v>369800</v>
+        <v>210100</v>
       </c>
       <c r="H23" s="3">
-        <v>394900</v>
+        <v>376200</v>
       </c>
       <c r="I23" s="3">
-        <v>314700</v>
+        <v>385600</v>
       </c>
       <c r="J23" s="3">
+        <v>307600</v>
+      </c>
+      <c r="K23" s="3">
         <v>293400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>290200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>128700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>121100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>82900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>72200</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>63000</v>
+        <v>117700</v>
       </c>
       <c r="E24" s="3">
-        <v>22100</v>
+        <v>62000</v>
       </c>
       <c r="F24" s="3">
-        <v>39800</v>
+        <v>20700</v>
       </c>
       <c r="G24" s="3">
-        <v>93700</v>
+        <v>38400</v>
       </c>
       <c r="H24" s="3">
-        <v>83100</v>
+        <v>95300</v>
       </c>
       <c r="I24" s="3">
-        <v>62800</v>
+        <v>81100</v>
       </c>
       <c r="J24" s="3">
+        <v>61400</v>
+      </c>
+      <c r="K24" s="3">
         <v>41000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23700</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>326700</v>
+        <v>432500</v>
       </c>
       <c r="E26" s="3">
-        <v>339000</v>
+        <v>321400</v>
       </c>
       <c r="F26" s="3">
-        <v>178100</v>
+        <v>317300</v>
       </c>
       <c r="G26" s="3">
-        <v>276100</v>
+        <v>171700</v>
       </c>
       <c r="H26" s="3">
-        <v>311800</v>
+        <v>280900</v>
       </c>
       <c r="I26" s="3">
-        <v>251900</v>
+        <v>304500</v>
       </c>
       <c r="J26" s="3">
+        <v>246200</v>
+      </c>
+      <c r="K26" s="3">
         <v>252300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>263100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>109600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>106000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>82100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>48500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>275000</v>
+        <v>357100</v>
       </c>
       <c r="E27" s="3">
-        <v>292100</v>
+        <v>270500</v>
       </c>
       <c r="F27" s="3">
-        <v>138700</v>
+        <v>273400</v>
       </c>
       <c r="G27" s="3">
-        <v>237700</v>
+        <v>133700</v>
       </c>
       <c r="H27" s="3">
-        <v>272000</v>
+        <v>241800</v>
       </c>
       <c r="I27" s="3">
-        <v>228500</v>
+        <v>265600</v>
       </c>
       <c r="J27" s="3">
+        <v>223000</v>
+      </c>
+      <c r="K27" s="3">
         <v>249400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>263000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>109600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>106000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>82100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>48500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,38 +1580,41 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-400</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-1100</v>
-      </c>
-      <c r="L29" s="3">
-        <v>-100</v>
       </c>
       <c r="M29" s="3">
         <v>-100</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>-100</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>38400</v>
+        <v>-95700</v>
       </c>
       <c r="E32" s="3">
-        <v>-11600</v>
+        <v>-42900</v>
       </c>
       <c r="F32" s="3">
-        <v>47800</v>
+        <v>21300</v>
       </c>
       <c r="G32" s="3">
-        <v>-83000</v>
+        <v>-68500</v>
       </c>
       <c r="H32" s="3">
-        <v>-82400</v>
+        <v>-18100</v>
       </c>
       <c r="I32" s="3">
-        <v>-39600</v>
+        <v>11400</v>
       </c>
       <c r="J32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-47600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-46900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-19800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>55500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>275000</v>
+        <v>357100</v>
       </c>
       <c r="E33" s="3">
-        <v>292100</v>
+        <v>270500</v>
       </c>
       <c r="F33" s="3">
-        <v>138700</v>
+        <v>273400</v>
       </c>
       <c r="G33" s="3">
-        <v>237700</v>
+        <v>133700</v>
       </c>
       <c r="H33" s="3">
-        <v>272000</v>
+        <v>241800</v>
       </c>
       <c r="I33" s="3">
-        <v>228100</v>
+        <v>265600</v>
       </c>
       <c r="J33" s="3">
+        <v>223000</v>
+      </c>
+      <c r="K33" s="3">
         <v>249400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>262000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>109500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>105900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>82000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>48400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>275000</v>
+        <v>357100</v>
       </c>
       <c r="E35" s="3">
-        <v>292100</v>
+        <v>270500</v>
       </c>
       <c r="F35" s="3">
-        <v>138700</v>
+        <v>273400</v>
       </c>
       <c r="G35" s="3">
-        <v>237700</v>
+        <v>133700</v>
       </c>
       <c r="H35" s="3">
-        <v>272000</v>
+        <v>241800</v>
       </c>
       <c r="I35" s="3">
-        <v>228100</v>
+        <v>265600</v>
       </c>
       <c r="J35" s="3">
+        <v>223000</v>
+      </c>
+      <c r="K35" s="3">
         <v>249400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>262000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>109500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>105900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>82000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>48400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>44600</v>
+        <v>265700</v>
       </c>
       <c r="E41" s="3">
-        <v>138500</v>
+        <v>43900</v>
       </c>
       <c r="F41" s="3">
-        <v>59000</v>
+        <v>129600</v>
       </c>
       <c r="G41" s="3">
-        <v>25300</v>
+        <v>56900</v>
       </c>
       <c r="H41" s="3">
-        <v>11700</v>
+        <v>25800</v>
       </c>
       <c r="I41" s="3">
-        <v>23800</v>
+        <v>11400</v>
       </c>
       <c r="J41" s="3">
+        <v>23300</v>
+      </c>
+      <c r="K41" s="3">
         <v>800900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>580300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3800</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1067500</v>
+        <v>661000</v>
       </c>
       <c r="E42" s="3">
-        <v>1187800</v>
+        <v>617400</v>
       </c>
       <c r="F42" s="3">
-        <v>1241400</v>
+        <v>631300</v>
       </c>
       <c r="G42" s="3">
-        <v>1480100</v>
+        <v>719500</v>
       </c>
       <c r="H42" s="3">
-        <v>1301300</v>
+        <v>894400</v>
       </c>
       <c r="I42" s="3">
-        <v>1081600</v>
+        <v>712700</v>
       </c>
       <c r="J42" s="3">
+        <v>449300</v>
+      </c>
+      <c r="K42" s="3">
         <v>727400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>499500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>446500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>287700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>158300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>142400</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>130400</v>
+        <v>85200</v>
       </c>
       <c r="E43" s="3">
-        <v>138800</v>
+        <v>128300</v>
       </c>
       <c r="F43" s="3">
-        <v>74500</v>
+        <v>129900</v>
       </c>
       <c r="G43" s="3">
-        <v>87400</v>
+        <v>71900</v>
       </c>
       <c r="H43" s="3">
-        <v>81900</v>
+        <v>93000</v>
       </c>
       <c r="I43" s="3">
-        <v>129300</v>
+        <v>83800</v>
       </c>
       <c r="J43" s="3">
+        <v>126300</v>
+      </c>
+      <c r="K43" s="3">
         <v>232600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>174100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>40100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>45000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>77500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20300</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9400</v>
+        <v>12000</v>
       </c>
       <c r="E44" s="3">
-        <v>8000</v>
+        <v>9200</v>
       </c>
       <c r="F44" s="3">
-        <v>7100</v>
+        <v>7500</v>
       </c>
       <c r="G44" s="3">
-        <v>7700</v>
+        <v>6900</v>
       </c>
       <c r="H44" s="3">
         <v>6100</v>
       </c>
       <c r="I44" s="3">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="J44" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K44" s="3">
         <v>8300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4100</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13000</v>
+        <v>499100</v>
       </c>
       <c r="E45" s="3">
-        <v>15800</v>
+        <v>445400</v>
       </c>
       <c r="F45" s="3">
-        <v>12200</v>
+        <v>495100</v>
       </c>
       <c r="G45" s="3">
-        <v>23800</v>
+        <v>489300</v>
       </c>
       <c r="H45" s="3">
-        <v>10200</v>
+        <v>635400</v>
       </c>
       <c r="I45" s="3">
-        <v>26100</v>
+        <v>567800</v>
       </c>
       <c r="J45" s="3">
+        <v>633300</v>
+      </c>
+      <c r="K45" s="3">
         <v>71700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7900</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1264900</v>
+        <v>1523100</v>
       </c>
       <c r="E46" s="3">
-        <v>1488900</v>
+        <v>1244200</v>
       </c>
       <c r="F46" s="3">
-        <v>1394400</v>
+        <v>1393400</v>
       </c>
       <c r="G46" s="3">
-        <v>1626600</v>
+        <v>1344500</v>
       </c>
       <c r="H46" s="3">
-        <v>1414200</v>
+        <v>1654700</v>
       </c>
       <c r="I46" s="3">
-        <v>1266100</v>
+        <v>1380800</v>
       </c>
       <c r="J46" s="3">
+        <v>1237500</v>
+      </c>
+      <c r="K46" s="3">
         <v>923300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>650500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>498400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>181200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>131400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>178600</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>162500</v>
+        <v>151000</v>
       </c>
       <c r="E47" s="3">
-        <v>158300</v>
+        <v>133500</v>
       </c>
       <c r="F47" s="3">
-        <v>189600</v>
+        <v>112100</v>
       </c>
       <c r="G47" s="3">
-        <v>99800</v>
+        <v>109500</v>
       </c>
       <c r="H47" s="3">
-        <v>149600</v>
+        <v>51800</v>
       </c>
       <c r="I47" s="3">
-        <v>219700</v>
+        <v>100500</v>
       </c>
       <c r="J47" s="3">
+        <v>187400</v>
+      </c>
+      <c r="K47" s="3">
         <v>201900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>199300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>115700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>82800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>101500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>86200</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>144400</v>
+        <v>163400</v>
       </c>
       <c r="E48" s="3">
-        <v>128900</v>
+        <v>142100</v>
       </c>
       <c r="F48" s="3">
-        <v>58500</v>
+        <v>112800</v>
       </c>
       <c r="G48" s="3">
-        <v>60300</v>
+        <v>49400</v>
       </c>
       <c r="H48" s="3">
-        <v>54700</v>
+        <v>54900</v>
       </c>
       <c r="I48" s="3">
-        <v>55100</v>
+        <v>47900</v>
       </c>
       <c r="J48" s="3">
+        <v>48500</v>
+      </c>
+      <c r="K48" s="3">
         <v>110300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>100100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>60900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>70300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36700</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2069700</v>
+        <v>2369100</v>
       </c>
       <c r="E49" s="3">
-        <v>2037100</v>
+        <v>2035800</v>
       </c>
       <c r="F49" s="3">
-        <v>2091400</v>
+        <v>1905100</v>
       </c>
       <c r="G49" s="3">
-        <v>2061600</v>
+        <v>2015000</v>
       </c>
       <c r="H49" s="3">
-        <v>2412300</v>
+        <v>2097200</v>
       </c>
       <c r="I49" s="3">
-        <v>989500</v>
+        <v>1270800</v>
       </c>
       <c r="J49" s="3">
+        <v>967100</v>
+      </c>
+      <c r="K49" s="3">
         <v>1732900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1692900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1255300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1644800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>927300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>385500</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>242700</v>
+        <v>58800</v>
       </c>
       <c r="E52" s="3">
-        <v>191900</v>
+        <v>65900</v>
       </c>
       <c r="F52" s="3">
-        <v>176300</v>
+        <v>52400</v>
       </c>
       <c r="G52" s="3">
-        <v>120700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>104000</v>
+        <v>34400</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I52" s="3">
-        <v>72000</v>
+        <v>63400</v>
       </c>
       <c r="J52" s="3">
+        <v>35700</v>
+      </c>
+      <c r="K52" s="3">
         <v>89900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>93500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>120400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>121300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>114800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>41600</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3884300</v>
+        <v>4549300</v>
       </c>
       <c r="E54" s="3">
-        <v>4005100</v>
+        <v>3820600</v>
       </c>
       <c r="F54" s="3">
-        <v>3910100</v>
+        <v>3748400</v>
       </c>
       <c r="G54" s="3">
-        <v>3969000</v>
+        <v>3730400</v>
       </c>
       <c r="H54" s="3">
-        <v>3023900</v>
+        <v>3991200</v>
       </c>
       <c r="I54" s="3">
-        <v>2602400</v>
+        <v>2952500</v>
       </c>
       <c r="J54" s="3">
+        <v>2543600</v>
+      </c>
+      <c r="K54" s="3">
         <v>2130300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1814400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1347000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>905400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>748800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>728600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>32100</v>
+        <v>34300</v>
       </c>
       <c r="E57" s="3">
-        <v>30700</v>
+        <v>31600</v>
       </c>
       <c r="F57" s="3">
-        <v>33400</v>
+        <v>28800</v>
       </c>
       <c r="G57" s="3">
-        <v>32000</v>
+        <v>32200</v>
       </c>
       <c r="H57" s="3">
-        <v>22200</v>
+        <v>32600</v>
       </c>
       <c r="I57" s="3">
-        <v>12400</v>
+        <v>21700</v>
       </c>
       <c r="J57" s="3">
+        <v>12100</v>
+      </c>
+      <c r="K57" s="3">
         <v>13600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3200</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>34600</v>
+        <v>72100</v>
       </c>
       <c r="E58" s="3">
-        <v>28200</v>
+        <v>49500</v>
       </c>
       <c r="F58" s="3">
-        <v>21000</v>
+        <v>45400</v>
       </c>
       <c r="G58" s="3">
-        <v>11700</v>
+        <v>40900</v>
       </c>
       <c r="H58" s="3">
-        <v>19900</v>
+        <v>16000</v>
       </c>
       <c r="I58" s="3">
-        <v>36900</v>
+        <v>19500</v>
       </c>
       <c r="J58" s="3">
+        <v>36100</v>
+      </c>
+      <c r="K58" s="3">
         <v>61100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>63300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>26300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>42100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15600</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>188700</v>
+        <v>192900</v>
       </c>
       <c r="E59" s="3">
-        <v>154900</v>
+        <v>161500</v>
       </c>
       <c r="F59" s="3">
-        <v>132000</v>
+        <v>119700</v>
       </c>
       <c r="G59" s="3">
-        <v>277800</v>
+        <v>99000</v>
       </c>
       <c r="H59" s="3">
-        <v>243700</v>
+        <v>266700</v>
       </c>
       <c r="I59" s="3">
-        <v>108400</v>
+        <v>234800</v>
       </c>
       <c r="J59" s="3">
+        <v>104300</v>
+      </c>
+      <c r="K59" s="3">
         <v>111700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>190700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>63700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>41100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28100</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>255500</v>
+        <v>316000</v>
       </c>
       <c r="E60" s="3">
-        <v>213800</v>
+        <v>251300</v>
       </c>
       <c r="F60" s="3">
-        <v>186300</v>
+        <v>200100</v>
       </c>
       <c r="G60" s="3">
-        <v>321500</v>
+        <v>179600</v>
       </c>
       <c r="H60" s="3">
-        <v>285800</v>
+        <v>327100</v>
       </c>
       <c r="I60" s="3">
-        <v>157700</v>
+        <v>279100</v>
       </c>
       <c r="J60" s="3">
+        <v>154200</v>
+      </c>
+      <c r="K60" s="3">
         <v>144800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>187100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>78400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>68000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>66100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>46900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>772500</v>
+        <v>789900</v>
       </c>
       <c r="E61" s="3">
-        <v>801100</v>
+        <v>759900</v>
       </c>
       <c r="F61" s="3">
-        <v>824800</v>
+        <v>749800</v>
       </c>
       <c r="G61" s="3">
-        <v>895200</v>
+        <v>795300</v>
       </c>
       <c r="H61" s="3">
-        <v>345900</v>
+        <v>910600</v>
       </c>
       <c r="I61" s="3">
-        <v>224300</v>
+        <v>337700</v>
       </c>
       <c r="J61" s="3">
+        <v>219200</v>
+      </c>
+      <c r="K61" s="3">
         <v>239000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>305800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>326500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>405000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>381700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>497000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>58600</v>
+        <v>43300</v>
       </c>
       <c r="E62" s="3">
-        <v>79100</v>
+        <v>50700</v>
       </c>
       <c r="F62" s="3">
-        <v>132500</v>
+        <v>59400</v>
       </c>
       <c r="G62" s="3">
-        <v>122300</v>
+        <v>70000</v>
       </c>
       <c r="H62" s="3">
-        <v>61600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>10600</v>
-      </c>
-      <c r="J62" s="3">
+        <v>63000</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>25100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1481300</v>
+        <v>1166600</v>
       </c>
       <c r="E66" s="3">
-        <v>1495800</v>
+        <v>1068900</v>
       </c>
       <c r="F66" s="3">
-        <v>1525700</v>
+        <v>1024000</v>
       </c>
       <c r="G66" s="3">
-        <v>1710100</v>
+        <v>1062900</v>
       </c>
       <c r="H66" s="3">
-        <v>943000</v>
+        <v>1315800</v>
       </c>
       <c r="I66" s="3">
-        <v>593300</v>
+        <v>676900</v>
       </c>
       <c r="J66" s="3">
+        <v>383700</v>
+      </c>
+      <c r="K66" s="3">
         <v>516200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>524100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>418400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>482800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>453300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>549700</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1689400</v>
+        <v>1615200</v>
       </c>
       <c r="E72" s="3">
-        <v>1638000</v>
+        <v>1192900</v>
       </c>
       <c r="F72" s="3">
-        <v>1450100</v>
+        <v>1086900</v>
       </c>
       <c r="G72" s="3">
-        <v>993400</v>
+        <v>938600</v>
       </c>
       <c r="H72" s="3">
-        <v>1112800</v>
+        <v>531100</v>
       </c>
       <c r="I72" s="3">
-        <v>1287800</v>
+        <v>683000</v>
       </c>
       <c r="J72" s="3">
+        <v>867400</v>
+      </c>
+      <c r="K72" s="3">
         <v>1693000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1148600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>585700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>407400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>279400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50100</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2403000</v>
+        <v>2924700</v>
       </c>
       <c r="E76" s="3">
-        <v>2509200</v>
+        <v>2363600</v>
       </c>
       <c r="F76" s="3">
-        <v>2384400</v>
+        <v>2348400</v>
       </c>
       <c r="G76" s="3">
-        <v>2258900</v>
+        <v>2299100</v>
       </c>
       <c r="H76" s="3">
-        <v>2080900</v>
+        <v>2297800</v>
       </c>
       <c r="I76" s="3">
-        <v>2009100</v>
+        <v>2031700</v>
       </c>
       <c r="J76" s="3">
+        <v>1963700</v>
+      </c>
+      <c r="K76" s="3">
         <v>1614100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1290300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>928700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>422600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>295500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>178900</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>275000</v>
+        <v>357100</v>
       </c>
       <c r="E81" s="3">
-        <v>292100</v>
+        <v>270500</v>
       </c>
       <c r="F81" s="3">
-        <v>138700</v>
+        <v>273400</v>
       </c>
       <c r="G81" s="3">
-        <v>237700</v>
+        <v>133700</v>
       </c>
       <c r="H81" s="3">
-        <v>272000</v>
+        <v>241800</v>
       </c>
       <c r="I81" s="3">
-        <v>228100</v>
+        <v>265600</v>
       </c>
       <c r="J81" s="3">
+        <v>223000</v>
+      </c>
+      <c r="K81" s="3">
         <v>249400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>262000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>109500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>105900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>82000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>48400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,35 +3687,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>63600</v>
+        <v>10000</v>
       </c>
       <c r="E83" s="3">
-        <v>56200</v>
+        <v>11400</v>
       </c>
       <c r="F83" s="3">
-        <v>45000</v>
+        <v>-2100</v>
       </c>
       <c r="G83" s="3">
-        <v>36000</v>
+        <v>700</v>
       </c>
       <c r="H83" s="3">
-        <v>23700</v>
+        <v>6300</v>
       </c>
       <c r="I83" s="3">
-        <v>22100</v>
+        <v>5600</v>
       </c>
       <c r="J83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K83" s="3">
         <v>19300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3531,9 +3729,12 @@
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>487700</v>
+        <v>612200</v>
       </c>
       <c r="E89" s="3">
-        <v>346900</v>
+        <v>479700</v>
       </c>
       <c r="F89" s="3">
-        <v>214100</v>
+        <v>324700</v>
       </c>
       <c r="G89" s="3">
-        <v>-92000</v>
+        <v>206400</v>
       </c>
       <c r="H89" s="3">
-        <v>399600</v>
+        <v>-93600</v>
       </c>
       <c r="I89" s="3">
-        <v>243300</v>
+        <v>390200</v>
       </c>
       <c r="J89" s="3">
+        <v>273400</v>
+      </c>
+      <c r="K89" s="3">
         <v>311500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>269000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>177600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>173900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>92100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>123900</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-29200</v>
+        <v>-9100</v>
       </c>
       <c r="E91" s="3">
-        <v>-66100</v>
+        <v>-28700</v>
       </c>
       <c r="F91" s="3">
+        <v>-61900</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
-      <c r="G91" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-28600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,36 +4153,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>56100</v>
+        <v>15800</v>
       </c>
       <c r="E94" s="3">
-        <v>62900</v>
+        <v>55200</v>
       </c>
       <c r="F94" s="3">
-        <v>167800</v>
+        <v>58900</v>
       </c>
       <c r="G94" s="3">
-        <v>-53800</v>
+        <v>161800</v>
       </c>
       <c r="H94" s="3">
-        <v>-264200</v>
+        <v>-54700</v>
       </c>
       <c r="I94" s="3">
-        <v>-451400</v>
+        <v>-257900</v>
       </c>
       <c r="J94" s="3">
+        <v>-475800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-397400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
@@ -3969,9 +4198,12 @@
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,35 +4220,36 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-156400</v>
+        <v>118300</v>
       </c>
       <c r="E96" s="3">
-        <v>-104200</v>
+        <v>153800</v>
       </c>
       <c r="F96" s="3">
-        <v>-104200</v>
+        <v>97600</v>
       </c>
       <c r="G96" s="3">
-        <v>-104200</v>
+        <v>100500</v>
       </c>
       <c r="H96" s="3">
-        <v>-104200</v>
+        <v>106000</v>
       </c>
       <c r="I96" s="3">
-        <v>-41700</v>
+        <v>101800</v>
       </c>
       <c r="J96" s="3">
+        <v>40800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-20800</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4029,9 +4262,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,36 +4397,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-637800</v>
+        <v>-412900</v>
       </c>
       <c r="E100" s="3">
-        <v>-349800</v>
+        <v>-627300</v>
       </c>
       <c r="F100" s="3">
-        <v>-279300</v>
+        <v>-327400</v>
       </c>
       <c r="G100" s="3">
-        <v>183000</v>
+        <v>-269300</v>
       </c>
       <c r="H100" s="3">
-        <v>-153400</v>
+        <v>186100</v>
       </c>
       <c r="I100" s="3">
-        <v>197600</v>
+        <v>-149800</v>
       </c>
       <c r="J100" s="3">
+        <v>184500</v>
+      </c>
+      <c r="K100" s="3">
         <v>134600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
@@ -4197,36 +4442,39 @@
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>-101700</v>
       </c>
       <c r="E101" s="3">
-        <v>19400</v>
+        <v>-48900</v>
       </c>
       <c r="F101" s="3">
-        <v>-68900</v>
+        <v>18200</v>
       </c>
       <c r="G101" s="3">
-        <v>-23600</v>
+        <v>-66400</v>
       </c>
       <c r="H101" s="3">
-        <v>5700</v>
+        <v>-24000</v>
       </c>
       <c r="I101" s="3">
-        <v>353700</v>
+        <v>5600</v>
       </c>
       <c r="J101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K101" s="3">
         <v>209200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
@@ -4239,49 +4487,55 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-93900</v>
+        <v>113400</v>
       </c>
       <c r="E102" s="3">
-        <v>79500</v>
+        <v>-141300</v>
       </c>
       <c r="F102" s="3">
-        <v>33700</v>
+        <v>74400</v>
       </c>
       <c r="G102" s="3">
-        <v>13600</v>
+        <v>32500</v>
       </c>
       <c r="H102" s="3">
-        <v>-12200</v>
+        <v>13800</v>
       </c>
       <c r="I102" s="3">
-        <v>343100</v>
+        <v>-11900</v>
       </c>
       <c r="J102" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="K102" s="3">
         <v>257800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>2200</v>
       </c>
       <c r="M102" s="3">
         <v>2200</v>
       </c>
       <c r="N102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>PUODY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>892800</v>
+      </c>
+      <c r="E8" s="3">
         <v>918700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>735200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>605800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>499200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>638900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>619500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>509800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>549300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>592400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>334500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>281600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>206700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>215400</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E9" s="3">
         <v>332000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>303500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>272300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>240800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>295200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>281400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>210800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>245100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>312800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>152200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>120800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>81100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>86000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>527800</v>
+      </c>
+      <c r="E10" s="3">
         <v>586700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>431700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>333500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>258400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>343700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>338200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>299000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>304200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>279700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>182300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>160800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>125700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>129400</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,18 +979,21 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>3300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
@@ -990,8 +1009,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1008,42 +1027,45 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E15" s="3">
         <v>700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>368300</v>
+      </c>
+      <c r="E17" s="3">
         <v>337200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>314000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>278700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>243000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>298400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>281400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>207800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>242000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>307400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>146300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>118600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>81800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>87700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>524600</v>
+      </c>
+      <c r="E18" s="3">
         <v>581600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>421200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>327200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>256200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>340500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>338100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>302000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>307300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>285000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>188100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>163000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>125000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>127700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,83 +1211,87 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E20" s="3">
         <v>95700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>42900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-21300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>68500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>18100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-11400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>47600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>46900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>19800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-55500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>620300</v>
+      </c>
+      <c r="E21" s="3">
         <v>486600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>378900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>348900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>187900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>322500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>350000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>328600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>373800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1268,144 +1304,156 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E22" s="3">
         <v>151100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>154700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>124000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>71200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>57600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>33200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>61500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>41700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>79200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>54800</v>
       </c>
       <c r="O22" s="3">
         <v>54800</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>54800</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>664900</v>
+      </c>
+      <c r="E23" s="3">
         <v>550200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>383400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>338000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>210100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>376200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>385600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>307600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>293400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>290200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>128700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>121100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>82900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>72200</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>149900</v>
+      </c>
+      <c r="E24" s="3">
         <v>117700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>62000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>38400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>95300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>81100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>61400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>41000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23700</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>515100</v>
+      </c>
+      <c r="E26" s="3">
         <v>432500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>321400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>317300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>171700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>280900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>304500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>246200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>252300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>263100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>109600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>106000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>82100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>48500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>439200</v>
+      </c>
+      <c r="E27" s="3">
         <v>357100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>270500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>273400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>133700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>241800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>265600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>223000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>249400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>263000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>109600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>106000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>82100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>48500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1608,16 +1668,16 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-400</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-1100</v>
-      </c>
-      <c r="M29" s="3">
-        <v>-100</v>
       </c>
       <c r="N29" s="3">
         <v>-100</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-95700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-42900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>21300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-68500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-18100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>11400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-47600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-46900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-19800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>55500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>439200</v>
+      </c>
+      <c r="E33" s="3">
         <v>357100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>270500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>273400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>133700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>241800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>265600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>223000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>249400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>262000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>109500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>105900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>82000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>48400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>439200</v>
+      </c>
+      <c r="E35" s="3">
         <v>357100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>270500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>273400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>133700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>241800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>265600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>223000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>249400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>262000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>109500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>105900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>82000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>48400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1378400</v>
+      </c>
+      <c r="E41" s="3">
         <v>265700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>43900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>129600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>56900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>800900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>580300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3800</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>661000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>617400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>631300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>719500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>894400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>712700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>449300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>727400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>499500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>446500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>287700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>158300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>142400</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E43" s="3">
         <v>85200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>128300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>129900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>71900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>93000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>83800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>126300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>232600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>174100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>40100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>45000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>77500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20300</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E44" s="3">
         <v>12000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4100</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>156400</v>
+      </c>
+      <c r="E45" s="3">
         <v>499100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>445400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>495100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>489300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>635400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>567800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>633300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>71700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7900</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1584600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1523100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1244200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1393400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1344500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1654700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1380800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1237500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>923300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>650500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>498400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>181200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>131400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>178600</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E47" s="3">
         <v>151000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>133500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>112100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>109500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>51800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>100500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>187400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>201900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>199300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>115700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>82800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>101500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>86200</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>141800</v>
+      </c>
+      <c r="E48" s="3">
         <v>163400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>142100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>112800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>49400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>47900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>48500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>110300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>40800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>60900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>70300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36700</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1998000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2369100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2035800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1905100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2015000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2097200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1270800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>967100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1732900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1692900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1255300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1644800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>927300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>385500</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E52" s="3">
         <v>58800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>65900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>52400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34400</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>63400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>89900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>93500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>120400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>121300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>114800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41600</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4003600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4549300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3820600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3748400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3730400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3991200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2952500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2543600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2130300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1814400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1347000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>905400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>748800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>728600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E57" s="3">
         <v>34300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3200</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E58" s="3">
         <v>72100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>49500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>40900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>36100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>61100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>63300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>26300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>36000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>42100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>15600</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>211600</v>
+      </c>
+      <c r="E59" s="3">
         <v>192900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>161500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>119700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>99000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>266700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>234800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>104300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>111700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>190700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>63700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>41100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>55500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>28100</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>297800</v>
+      </c>
+      <c r="E60" s="3">
         <v>316000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>251300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>200100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>179600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>327100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>279100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>154200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>144800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>187100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>78400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>68000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>66100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>46900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>532000</v>
+      </c>
+      <c r="E61" s="3">
         <v>789900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>759900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>749800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>795300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>910600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>337700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>219200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>239000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>305800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>326500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>405000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>381700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>497000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E62" s="3">
         <v>43300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>50700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>59400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>70000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>63000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>25100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>872000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1166600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1068900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1024000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1062900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1315800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>676900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>383700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>516200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>524100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>418400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>482800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>453300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>549700</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1417600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1615200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1192900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1086900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>938600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>531100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>683000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>867400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1693000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1148600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>585700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>407400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>279400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50100</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2730800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2924700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2363600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2348400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2299100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2297800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2031700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1963700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1614100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1290300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>928700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>422600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>295500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>178900</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>439200</v>
+      </c>
+      <c r="E81" s="3">
         <v>357100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>270500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>273400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>133700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>241800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>265600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>223000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>249400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>262000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>109500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>105900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>82000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>48400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,38 +3885,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E83" s="3">
         <v>10000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-2100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>19300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3732,9 +3930,12 @@
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>395100</v>
+      </c>
+      <c r="E89" s="3">
         <v>612200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>479700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>324700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>206400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-93600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>390200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>273400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>311500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>269000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>177600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>173900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>92100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>123900</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-61900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,39 +4382,42 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-113700</v>
+      </c>
+      <c r="E94" s="3">
         <v>15800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>55200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>58900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>161800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-54700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-257900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-475800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-397400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
@@ -4201,9 +4430,12 @@
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,38 +4453,39 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E96" s="3">
         <v>118300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>153800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>97600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>100500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>106000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>101800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>40800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-20800</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,39 +4642,42 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-256800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-412900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-627300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-327400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-269300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>186100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-149800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>184500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>134600</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
@@ -4445,39 +4690,42 @@
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-101700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-48900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>18200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-66400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-24000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>7000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>209200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
@@ -4490,52 +4738,58 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>148600</v>
+      </c>
+      <c r="E102" s="3">
         <v>113400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-141300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>74400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>32500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>257800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13400</v>
-      </c>
-      <c r="M102" s="3">
-        <v>2200</v>
       </c>
       <c r="N102" s="3">
         <v>2200</v>
       </c>
       <c r="O102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>PUODY</t>
   </si>
@@ -988,11 +988,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>3300</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1037,7 +1037,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>52900</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
         <v>700</v>
@@ -1105,7 +1105,7 @@
         <v>368300</v>
       </c>
       <c r="E17" s="3">
-        <v>337200</v>
+        <v>340500</v>
       </c>
       <c r="F17" s="3">
         <v>314000</v>
@@ -1150,10 +1150,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>524600</v>
+        <v>524500</v>
       </c>
       <c r="E18" s="3">
-        <v>581600</v>
+        <v>578300</v>
       </c>
       <c r="F18" s="3">
         <v>421200</v>
@@ -1218,7 +1218,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-42800</v>
+        <v>-94500</v>
       </c>
       <c r="E20" s="3">
         <v>95700</v>
@@ -1266,10 +1266,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>620300</v>
+        <v>619900</v>
       </c>
       <c r="E21" s="3">
-        <v>486600</v>
+        <v>483300</v>
       </c>
       <c r="F21" s="3">
         <v>378900</v>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>65200</v>
+        <v>139100</v>
       </c>
       <c r="E22" s="3">
         <v>151100</v>
@@ -1410,7 +1410,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>149900</v>
+        <v>147600</v>
       </c>
       <c r="E24" s="3">
         <v>117700</v>
@@ -1506,7 +1506,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>515100</v>
+        <v>517300</v>
       </c>
       <c r="E26" s="3">
         <v>432500</v>
@@ -1554,7 +1554,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>439200</v>
+        <v>440900</v>
       </c>
       <c r="E27" s="3">
         <v>357100</v>
@@ -1794,7 +1794,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>42800</v>
+        <v>94500</v>
       </c>
       <c r="E32" s="3">
         <v>-95700</v>
@@ -1842,7 +1842,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>439200</v>
+        <v>440900</v>
       </c>
       <c r="E33" s="3">
         <v>357100</v>
@@ -1938,7 +1938,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>439200</v>
+        <v>440900</v>
       </c>
       <c r="E35" s="3">
         <v>357100</v>
@@ -2079,7 +2079,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1378400</v>
+        <v>247000</v>
       </c>
       <c r="E41" s="3">
         <v>265700</v>
@@ -2127,7 +2127,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>581500</v>
       </c>
       <c r="E42" s="3">
         <v>661000</v>
@@ -2175,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>41100</v>
+        <v>57700</v>
       </c>
       <c r="E43" s="3">
         <v>85200</v>
@@ -2271,7 +2271,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>156400</v>
+        <v>584200</v>
       </c>
       <c r="E45" s="3">
         <v>499100</v>
@@ -2319,7 +2319,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1584600</v>
+        <v>1479100</v>
       </c>
       <c r="E46" s="3">
         <v>1523100</v>
@@ -2367,7 +2367,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>49900</v>
+        <v>134300</v>
       </c>
       <c r="E47" s="3">
         <v>151000</v>
@@ -2607,7 +2607,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>24400</v>
+        <v>53700</v>
       </c>
       <c r="E52" s="3">
         <v>58800</v>
@@ -2703,7 +2703,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4003600</v>
+        <v>4009100</v>
       </c>
       <c r="E54" s="3">
         <v>4549300</v>
@@ -2839,7 +2839,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>56500</v>
+        <v>64600</v>
       </c>
       <c r="E58" s="3">
         <v>72100</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>211600</v>
+        <v>197200</v>
       </c>
       <c r="E59" s="3">
         <v>192900</v>
@@ -2935,7 +2935,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>297800</v>
+        <v>302100</v>
       </c>
       <c r="E60" s="3">
         <v>316000</v>
@@ -2983,7 +2983,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>532000</v>
+        <v>527700</v>
       </c>
       <c r="E61" s="3">
         <v>789900</v>
@@ -3223,7 +3223,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>872000</v>
+        <v>871000</v>
       </c>
       <c r="E66" s="3">
         <v>1166600</v>
@@ -3483,7 +3483,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1417600</v>
+        <v>1419300</v>
       </c>
       <c r="E72" s="3">
         <v>1615200</v>
@@ -3675,7 +3675,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2730800</v>
+        <v>2736300</v>
       </c>
       <c r="E76" s="3">
         <v>2924700</v>
@@ -3824,7 +3824,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>439200</v>
+        <v>440900</v>
       </c>
       <c r="E81" s="3">
         <v>357100</v>
@@ -3892,10 +3892,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12700</v>
+        <v>11500</v>
       </c>
       <c r="E83" s="3">
-        <v>10000</v>
+        <v>10800</v>
       </c>
       <c r="F83" s="3">
         <v>11400</v>
@@ -4180,10 +4180,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>395100</v>
+        <v>367700</v>
       </c>
       <c r="E89" s="3">
-        <v>612200</v>
+        <v>613000</v>
       </c>
       <c r="F89" s="3">
         <v>479700</v>
@@ -4251,7 +4251,7 @@
         <v>-54700</v>
       </c>
       <c r="E91" s="3">
-        <v>-9100</v>
+        <v>-9700</v>
       </c>
       <c r="F91" s="3">
         <v>-28700</v>
@@ -4392,10 +4392,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-113700</v>
+        <v>11400</v>
       </c>
       <c r="E94" s="3">
-        <v>15800</v>
+        <v>15200</v>
       </c>
       <c r="F94" s="3">
         <v>55200</v>
@@ -4460,7 +4460,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>96000</v>
+        <v>48000</v>
       </c>
       <c r="E96" s="3">
         <v>118300</v>
@@ -4652,10 +4652,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-256800</v>
+        <v>-347600</v>
       </c>
       <c r="E100" s="3">
-        <v>-412900</v>
+        <v>-413100</v>
       </c>
       <c r="F100" s="3">
         <v>-627300</v>
@@ -4699,14 +4699,14 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>123900</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-101700</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-48900</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G101" s="3">
         <v>18200</v>
@@ -4748,13 +4748,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>148600</v>
+        <v>31500</v>
       </c>
       <c r="E102" s="3">
-        <v>113400</v>
+        <v>215100</v>
       </c>
       <c r="F102" s="3">
-        <v>-141300</v>
+        <v>-92400</v>
       </c>
       <c r="G102" s="3">
         <v>74400</v>

--- a/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PUODY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>PUODY</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1113500</v>
+      </c>
+      <c r="E8" s="3">
         <v>892800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>918700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>735200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>605800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>499200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>638900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>619500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>509800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>549300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>592400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>334500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>281600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>206700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>215400</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E9" s="3">
         <v>365000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>332000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>303500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>272300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>240800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>295200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>281400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>210800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>245100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>312800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>152200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>120800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>81100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>86000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>643500</v>
+      </c>
+      <c r="E10" s="3">
         <v>527800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>586700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>431700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>333500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>258400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>343700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>338200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>299000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>304200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>279700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>182300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>160800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>125700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>129400</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,9 +998,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1012,8 +1031,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1030,45 +1049,48 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-169900</v>
+      </c>
+      <c r="E17" s="3">
         <v>368300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>340500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>314000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>278700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>243000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>298400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>281400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>207800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>242000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>307400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>146300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>118600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>81800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>87700</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1283400</v>
+      </c>
+      <c r="E18" s="3">
         <v>524500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>578300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>421200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>327200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>256200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>340500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>338100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>302000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>307300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>285000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>188100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>163000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>125000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>127700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,89 +1244,93 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-94500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>95700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>42900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-21300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>68500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>18100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-11400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>47600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>46900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>19800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-55500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1164000</v>
+      </c>
+      <c r="E21" s="3">
         <v>619900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>483300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>378900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>348900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>187900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>322500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>350000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>328600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>373800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1307,153 +1343,165 @@
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>254600</v>
+      </c>
+      <c r="E22" s="3">
         <v>139100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>151100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>154700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>124000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>71200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>57600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>33000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>33200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>61500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>41700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>79200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>54800</v>
       </c>
       <c r="P22" s="3">
         <v>54800</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>54800</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1200800</v>
+      </c>
+      <c r="E23" s="3">
         <v>664900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>550200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>383400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>338000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>210100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>376200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>385600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>307600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>293400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>290200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>128700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>121100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>82900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>72200</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>294900</v>
+      </c>
+      <c r="E24" s="3">
         <v>147600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>117700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>62000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>20700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>95300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>81100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>61400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>41000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>27100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>23700</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>905900</v>
+      </c>
+      <c r="E26" s="3">
         <v>517300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>432500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>321400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>317300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>171700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>280900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>304500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>246200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>252300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>263100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>109600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>106000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>82100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>48500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>813400</v>
+      </c>
+      <c r="E27" s="3">
         <v>440900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>357100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>270500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>273400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>133700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>241800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>265600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>223000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>249400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>263000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>109600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>106000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>82100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>48500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1671,16 +1731,16 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-400</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-1100</v>
-      </c>
-      <c r="N29" s="3">
-        <v>-100</v>
       </c>
       <c r="O29" s="3">
         <v>-100</v>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-120400</v>
+      </c>
+      <c r="E32" s="3">
         <v>94500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-95700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-42900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>21300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-68500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-18100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>11400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-47600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-46900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-19800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>55500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>813400</v>
+      </c>
+      <c r="E33" s="3">
         <v>440900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>357100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>270500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>273400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>133700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>241800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>265600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>223000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>249400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>262000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>109500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>105900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>82000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>48400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>813400</v>
+      </c>
+      <c r="E35" s="3">
         <v>440900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>357100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>270500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>273400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>133700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>241800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>265600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>223000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>249400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>262000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>109500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>105900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>82000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>48400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>508500</v>
+      </c>
+      <c r="E41" s="3">
         <v>247000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>265700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>129600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>56900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>800900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>580300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3800</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1037700</v>
+      </c>
+      <c r="E42" s="3">
         <v>581500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>661000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>617400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>631300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>719500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>894400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>712700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>449300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>727400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>499500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>446500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>287700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>158300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>142400</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>99500</v>
+      </c>
+      <c r="E43" s="3">
         <v>57700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>85200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>128300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>129900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>71900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>93000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>83800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>126300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>232600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>174100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>40100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>45000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>77500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20300</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E44" s="3">
         <v>8700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>12000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4100</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>548800</v>
+      </c>
+      <c r="E45" s="3">
         <v>584200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>499100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>445400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>495100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>489300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>635400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>567800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>633300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>71700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7900</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2205300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1479100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1523100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1244200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1393400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1344500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1654700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1380800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1237500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>923300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>650500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>498400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>181200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>131400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>178600</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>132700</v>
+      </c>
+      <c r="E47" s="3">
         <v>134300</v>
       </c>
-      <c r="E47" s="3">
-        <v>151000</v>
-      </c>
       <c r="F47" s="3">
+        <v>180200</v>
+      </c>
+      <c r="G47" s="3">
         <v>133500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>112100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>109500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>51800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>100500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>187400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>201900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>199300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>115700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>82800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>101500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>86200</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>148400</v>
+      </c>
+      <c r="E48" s="3">
         <v>141800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>163400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>142100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>112800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>49400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>47900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>48500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>110300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>100100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>40800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>60900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>70300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36700</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2484600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1998000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2369100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2035800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1905100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2015000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2097200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1270800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>967100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1732900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1692900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1255300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1644800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>927300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>385500</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>53700</v>
+        <v>67000</v>
       </c>
       <c r="E52" s="3">
-        <v>58800</v>
+        <v>50400</v>
       </c>
       <c r="F52" s="3">
+        <v>26300</v>
+      </c>
+      <c r="G52" s="3">
         <v>65900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>52400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>34400</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>63400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>89900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>93500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>120400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>121300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>114800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>41600</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5298500</v>
+      </c>
+      <c r="E54" s="3">
         <v>4009100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4549300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3820600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3748400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3730400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3991200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2952500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2543600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2130300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1814400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1347000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>905400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>748800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>728600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E57" s="3">
         <v>29700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>34300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>32600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3200</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>145800</v>
+      </c>
+      <c r="E58" s="3">
         <v>64600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>72100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>49500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>40900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>19500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>36100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>61100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>63300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>26300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>36000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>42100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>15600</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>161700</v>
+      </c>
+      <c r="E59" s="3">
         <v>197200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>192900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>161500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>119700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>99000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>266700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>234800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>104300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>111700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>190700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>63700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>55500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28100</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>363600</v>
+      </c>
+      <c r="E60" s="3">
         <v>302100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>316000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>251300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>200100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>179600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>327100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>279100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>154200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>144800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>187100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>78400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>68000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>66100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>46900</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>539300</v>
+      </c>
+      <c r="E61" s="3">
         <v>527700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>789900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>759900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>749800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>795300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>910600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>337700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>219200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>239000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>305800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>326500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>405000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>381700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>497000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E62" s="3">
         <v>23800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>43300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>50700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>59400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>70000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>63000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>25100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>943700</v>
+      </c>
+      <c r="E66" s="3">
         <v>871000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1166600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1068900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1024000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1062900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1315800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>676900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>383700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>516200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>524100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>418400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>482800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>453300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>549700</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2287400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1419300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1615200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1192900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1086900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>938600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>531100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>683000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>867400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1693000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1148600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>585700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>407400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>279400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>50100</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3858900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2736300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2924700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2363600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2348400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2299100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2297800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2031700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1963700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1614100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1290300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>928700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>422600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>295500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>178900</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>813400</v>
+      </c>
+      <c r="E81" s="3">
         <v>440900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>357100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>270500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>273400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>133700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>241800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>265600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>223000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>249400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>262000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>109500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>105900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>82000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>48400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,41 +4083,42 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E83" s="3">
         <v>11500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-2100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3933,9 +4131,12 @@
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>493200</v>
+      </c>
+      <c r="E89" s="3">
         <v>367700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>613000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>479700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>324700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>206400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-93600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>390200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>273400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>311500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>269000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>177600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>173900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>92100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>123900</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-54700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-61900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1200</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,42 +4611,45 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>206600</v>
+      </c>
+      <c r="E94" s="3">
         <v>11400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>15200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>55200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>58900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>161800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-54700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-257900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-475800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-397400</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
@@ -4433,9 +4662,12 @@
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,41 +4686,42 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E96" s="3">
         <v>48000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>118300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>153800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>97600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>100500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>106000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>101800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>40800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-20800</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -4501,9 +4734,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,42 +4887,45 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-477300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-347600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-413100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-627300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-327400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-269300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>186100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-149800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>184500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>134600</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
@@ -4693,9 +4938,12 @@
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4708,27 +4956,27 @@
       <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3">
         <v>18200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-66400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-24000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>209200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
@@ -4741,55 +4989,61 @@
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>222500</v>
+      </c>
+      <c r="E102" s="3">
         <v>31500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>215100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-92400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>74400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>32500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>257800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13400</v>
-      </c>
-      <c r="N102" s="3">
-        <v>2200</v>
       </c>
       <c r="O102" s="3">
         <v>2200</v>
       </c>
       <c r="P102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
